--- a/research/brics_universities/output/BRICS_universities_uae.xlsx
+++ b/research/brics_universities/output/BRICS_universities_uae.xlsx
@@ -558,10 +558,10 @@
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>Prof. Dr. Awad AlKhalaf</t>
+          <t>Prof. Awad Husain AlKhalaf</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
@@ -5531,14 +5531,17 @@
           <t>• Учреждена правителем Шарджи (шейх Султан бин Мухаммад аль-Касими) — тип собственности «эмират Шарджа» вне стандартного списка, проверить
 • Сайт (SharePoint) не публикует адрес/телефон/e-mail в доступном HTML; контакты не найдены, поисковая квота исчерпана
 • Гуманитарно-исламский профиль — низкая релевантность для CubeSat-проекта
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Повторная проверка 04.10.2026: страница Board of Trustees называет канцлером HE Prof. Awad Husain AlKhalaf (без даты); председатель попечительского совета — HE Jamal Salim AL Turaifi. Страницы Contact us и External Cooperation пусты; в настройках сайта только шаблонные заглушки (12345, business@support.com) — не использовать
+• Перепроверка: Канцлер подтверждён на странице попечительского совета (без даты); контакты на сайте по-прежнему не опубликованы — уровень low сохранён</t>
         </is>
       </c>
       <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Https://www.alqasimia.ac.ae/en/AboutAQU/Pages/UniversityChancellor.aspx
 • Https://www.alqasimia.ac.ae/en
-• Nanosats.csv</t>
+• Nanosats.csv
+• Https://www.alqasimia.ac.ae/en/AboutAQU/Pages/BOT.aspx</t>
         </is>
       </c>
       <c r="AH20" s="4" t="inlineStr">
@@ -5809,7 +5812,9 @@
 • THE2027: в статусе Reporter (не ранжирован)
 • Info@aue.ae — из стороннего каталога, на официальном сайте не подтверждён
 • Председатель Попечительского совета — ген.-майор Ahmed Nasser Al-Raisi (по Википедии)
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• По поиску на aue.ae есть страница President's Message (aue.ae/presidents-message/) — открыть не удалось (403)
+• Перепроверка: 04.10.2026: aue.ae по-прежнему 403; президент Prof. Muthanna G. Abdul Razzaq подтверждается только поиском — данные не изменены</t>
         </is>
       </c>
       <c r="AG22" s="4" t="inlineStr">
@@ -6287,21 +6292,48 @@
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Emirates College for Advanced Education, P.O. Box 126662, Abu Dhabi, United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
+          <t>Emirates College for Advanced Education, Al Asayil St, Khalifa City (SE-43), Abu Dhabi, United Arab Emirates (P.O. Box 126662 — по Википедии, на сайте не указан)</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>info@ecae.ac.ae</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Dr. May Laith Al Taee
+Вице-канцлер (руководитель колледжа)
+Общий ящик колледжа
+Обращение: Dear Dr. Al Taee,</t>
+        </is>
+      </c>
       <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="inlineStr"/>
-      <c r="N26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>info@ecae.ac.ae</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>+971 2 509 9888</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
           <t>https://www.ecae.ac.ae</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>Dr. May Laith Al Taee</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>Vice Chancellor</t>
+        </is>
+      </c>
       <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="4" t="inlineStr"/>
@@ -6322,19 +6354,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE26" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF26" s="4" t="inlineStr">
         <is>
-          <t>• Сайт ecae.ac.ae недоступен (503 / нет ответа), архивных копий нет — контакты не проверены
-• По Википедии (дата не ясна): председатель — H.E. Sarah Yousef Al Amiri; Vice Chancellor — Dr. May Laith Al Taee; P.O. Box 126662 — требуется проверка на 2025–2026
+          <t>• Сайт ecae.ac.ae напрямую из нашей сети недоступен; страницы (главная, About us, Contact us) открыты через r.jina.ai 04.10.2026. Кампусы также в Аль-Айне и Аджмане (здания Teacher Training Institution Минобразования)
+• Председатель совета (по Википедии) — H.E. Sarah Yousef Al Amiri — на открытых страницах не проверено. Отдельный международный офис и его e-mail на сайте не найдены
 • Название на арабском дано по общепринятому написанию — проверить
 • Педагогический колледж (подготовка учителей) — релевантен только для образовательной/просветительской части проекта
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Перепроверка: Сайт ecae.ac.ae открыт через reader-сервис 04.10.2026: Vice Chancellor Dr. May Laith Al Taee, info@ecae.ac.ae, тел. +971 2 509 9888 и адрес кампуса (Khalifa City, Абу-Даби) подтверждены; дата страницы руководства не указана</t>
         </is>
       </c>
       <c r="AG26" s="4" t="inlineStr">
@@ -6399,10 +6436,24 @@
           <t>Fatima College of Health Sciences, Main Campus, Al Mafraq, Abu Dhabi, United Arab Emirates</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>info@fchs.ac.ae</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Fatima College of Health Sciences (general inbox, Abu Dhabi campus)
+Обращение: Dear Director of International Partnerships,</t>
+        </is>
+      </c>
       <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>info@fchs.ac.ae</t>
+        </is>
+      </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>+971 2 507 8765</t>
@@ -6435,24 +6486,30 @@
           <t>3</t>
         </is>
       </c>
-      <c r="AD27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
       <c r="AE27" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>• Учреждён в 2006 г. в системе ACTVET (Abu Dhabi Centre for Technical and Vocational Education and Training)
-• Кампусы: Абу-Даби (Al Mafraq), Эль-Айн (Al Maqam, +971 3 703 5555), Аль-Дафра (Madinat Zayed), Аджман
-• Сайт на JavaScript: e-mail и руководитель не найдены; main_fields — ориентировочно
-• Медицинский колледж; nanosats.csv (UAE): записей нет</t>
+• Кампусы (официальный сайт): Абу-Даби (Al Mafraq, +971 2 507 8765, info@fchs.ac.ae), Эль-Айн (Al Maqam, +971 3 703 5555, alain@fchs.ac.ae), Аль-Дафра (Madinat Zayed, +971 2 898 6915, aldhafra@fchs.ac.ae), Аджман (+971 6 701 7200, ajman@fchs.ac.ae)
+• Руководитель колледжа (декан/директор) на сайте не указан; main_fields — ориентировочно
+• Медицинский колледж; nanosats.csv (UAE): записей нет
+• Перепроверка: Общий e-mail info@fchs.ac.ae, телефон и кампусы подтверждены через официальный API сайта fchs.ac.ae (обновл. 06.2026); руководитель не найден</t>
         </is>
       </c>
       <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fchs.ac.ae/contact-us
-• Https://www.fchs.ac.ae/</t>
+• Https://www.fchs.ac.ae/
+• Https://www.fchs.ac.ae/api/campuses</t>
         </is>
       </c>
       <c r="AH27" s="4" t="inlineStr">
@@ -6627,7 +6684,11 @@
 • Media and Communication</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Liwa University, Saeed Bin Ahmed Al Otaiba Street (ex-Al Najda Street), Al Danah, Baniyas Tower B, P.O. Box 41009, Abu Dhabi, United Arab Emirates (по поисковому индексу lu.ac.ae; не открыто)</t>
+        </is>
+      </c>
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="4" t="inlineStr"/>
@@ -6640,7 +6701,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>Prof. Mohamed Dhiaf</t>
+          <t>Prof. Mohamed Mahjoub Dhiaf</t>
         </is>
       </c>
       <c r="Q29" s="4" t="inlineStr">
@@ -6676,10 +6737,11 @@
       </c>
       <c r="AF29" s="4" t="inlineStr">
         <is>
-          <t>• Сайт lu.ac.ae блокирует автоматический доступ (403) — контакты не проверены; по Википедии: P.O. Box 41009, Abu Dhabi, e-mail info@lc.ac.ae (старый домен Liwa College), тел. 600500606 — требуется проверка
-• Кампусы в Абу-Даби и Эль-Айне (новый кампус в Эль-Айне открыт в 2025)
+          <t>• Кампусы в Абу-Даби и Эль-Айне (новый кампус в Эль-Айне открыт в 2025)
 • Main_fields — ориентировочно, не проверены по сайту
-• THE2027: Reporter (без ранга); nanosats.csv (UAE): записей нет</t>
+• THE2027: Reporter (без ранга); nanosats.csv (UAE): записей нет
+• Сайт lu.ac.ae по-прежнему за Cloudflare (403, 04.10.2026). По поисковому индексу официальных страниц (lu.ac.ae/our-leadership, профиль вуза): президент Prof. Mohamed Mahjoub Dhiaf, адрес Baniyas Tower B, Al Danah, P.O. Box 41009, Abu Dhabi, тел. 600 500606; e-mail в сниппете скрыт — не внесён (старый info@lc.ac.ae из Википедии не использовать без проверки)
+• Перепроверка: Сайт закрыт Cloudflare; по поисковому индексу официальных страниц уточнены полное имя президента и адрес; e-mail не подтверждён</t>
         </is>
       </c>
       <c r="AG29" s="4" t="inlineStr">
@@ -8134,7 +8196,8 @@
         <is>
           <t>• Сайт uowdubai.ac.ae блокирует автоматический доступ (403) — e-mail, телефон и P.O. Box не проверены
 • Автономный кампус University of Wollongong (Австралия), президент с 2015 г
-• Main_fields — ориентировочно; nanosats.csv (UAE): записей нет</t>
+• Main_fields — ориентировочно; nanosats.csv (UAE): записей нет
+• Перепроверка: uowdubai.ac.ae (главная, /contact-us, sitemap) и WebFetch возвращают 403 — данные не изменены (04.10.2026)</t>
         </is>
       </c>
       <c r="AG40" s="4" t="inlineStr">

--- a/research/brics_universities/output/BRICS_universities_uae.xlsx
+++ b/research/brics_universities/output/BRICS_universities_uae.xlsx
@@ -12,8 +12,8 @@
     <sheet name="ОАЭ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AI$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ОАЭ'!$A$1:$AI$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AJ$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ОАЭ'!$A$1:$AJ$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата формирования: 2026-10-04</t>
+          <t>Дата формирования: 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -666,30 +666,31 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
-    <col width="60" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,120 +751,125 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Стыковка e-mail и адресата</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>E-mail (международный отдел)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>E-mail (общий / ректорат)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Ректор / президент</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг QS</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг THE</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Национальный рейтинг</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -930,47 +936,52 @@
 Обращение: Dear Dr. Al Najdawi,</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr"/>
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>info@ku.ac.ae</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+971 2 312 3333</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>https://www.ku.ac.ae</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>H.E. Prof. Ebrahim Al Hajri</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>QS2027: 147</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>THE2027: =235</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>• MYSAT-1 (2018)
 • MeznSat (2020)
@@ -978,17 +989,17 @@
 • Light-1 (2021)</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>6U CubeSat с собственной экологичной HTP-двигательной установкой (совместно с UAE Space Agency, запуск ожидался к концу 2026)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>Наземная станция KU Space Technology and Innovation Lab (указана на странице facilities; параметры не раскрыты)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>• Khalifa University Space Technology and Innovation Center (KUSTIC)
 • Khalifa University Space Technology and Innovation Lab (KUSTIL)
@@ -996,7 +1007,7 @@
 • Thermal vacuum chamber &amp; cleanroom</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency
 • Yahsat (Al Yah Satellite Communications)
@@ -1006,26 +1017,26 @@
 • American University of Ras Al Khaimah (MeznSat)</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AD2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Председатель Попечительского совета — Шейх Хамед бин Заед Аль Нахайян (H.H. Sheikh Hamed bin Zayed Al Nahyan); исполнительный глава — президент Prof. Ebrahim Al Hajri
 • Отдельный e-mail международного офиса не опубликован; isso@ku.ac.ae и studyabroad@ku.ac.ae — студенческие службы. Для партнёрства — info@ku.ac.ae; профильный руководитель — Dr. Ashraf Al Najdawi, Vice President, External Relations
@@ -1034,7 +1045,7 @@
 • QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ku.ac.ae/university-leadership
 • Https://www.ku.ac.ae/contact-us
@@ -1045,12 +1056,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1102,35 +1113,40 @@
       </c>
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+971 4 607 1200</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>https://www.mbrsc.ae</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>H.E. Salem Humaid AlMarri</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>Director General</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>• DubaiSat-1 (2009)
 • DubaiSat-2 (2013)
@@ -1146,19 +1162,19 @@
 • HCT-SAT 2 (2025)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• PHI-2…PHI-5 (12U, Payload Hosting Initiative, with NanoAvionics)
 • Emirates Airlock for NASA Lunar Gateway
 • Rashid rover programme</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>MBRSC ground station (Al Khawaneej, Dubai) — offers ground station services</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• Satellite Development Programme
 • UAE Astronaut Programme
@@ -1166,7 +1182,7 @@
 • Payload Hosting Initiative (PHI)</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• UNOOSA (PHI, 'Access to Space for All')
 • NASA (astronaut training, Lunar Gateway Emirates Airlock)
@@ -1176,22 +1192,22 @@
 • Satrec Initiative (DubaiSat, Etihad-SAT)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr"/>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Не университет, а государственное космическое агентство эмирата Дубай (включено намеренно); председатель — H.E. Hamad Obaid Al Mansoori
 • E-mail на официальном сайте не опубликован; сторонние источники (Bayut и др.) указывают info@mbrsc.ae — не проверено на официальной странице
@@ -1199,7 +1215,7 @@
 • Etihad-SAT: на сайте MBRSC указан запуск в марте 2025; HCT-SAT 2 и PHI-Demo — по nanosats.csv; Hope Probe — марсианский орбитальный аппарат (не CubeSat)</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mbrsc.ae/contact-us/
 • Https://www.mbrsc.ae/about/
@@ -1209,12 +1225,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1277,94 +1293,99 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>servicedesk@uaeu.ac.ae</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+971 3 701 7111</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>https://www.uaeu.ac.ae</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Ali Alraeesi</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>QS2027: 217</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>THE2027: =235</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>• ALainSat-1 (2025)
 • LEONAV-1 (2026)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>813 Satellite (Arab Satellite 813, EO, Arab cooperation project)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>NSSTC Ground Segment at UAEU (Al Ain): S/X-band dish antennas + UHF antenna</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>National Space Science and Technology Center (NSSTC)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (NSSTC co-founder)
 • Telecommunications and Digital Government Regulatory Authority (ICT Fund, NSSTC co-founder)
 • IEEE GRSS (AlAinSat-1 payloads)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AC4" s="5" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Канцлер (Chancellor) — H.E. Zaki Anwar Nusseibeh; исполнительный руководитель — вице-канцлер Prof. Ahmed Ali Alraeesi
 • Отдельный e-mail международного офиса на сайте не найден; servicedesk@uaeu.ac.ae — общий сервис-деск. Для космической тематики лучше параллельно писать в NSSTC: nsstc@uaeu.ac.ae
@@ -1372,7 +1393,7 @@
 • MeznSat (2020) построен Khalifa University и AURAK, не UAEU</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uaeu.ac.ae/en/contact/index.shtml
 • Https://www.uaeu.ac.ae/en/vc/index.shtml
@@ -1384,12 +1405,12 @@
 • Https://www.emirates247.com/uae/uaeu-announces-successful-launch-of-leonav-1-satellite/3485</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1455,66 +1476,71 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>OIR@sharjah.ac.ae</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>info@sharjah.ac.ae</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+971 6 558 5000</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>https://www.sharjah.ac.ae</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Prof. Esameldin Agamy</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>QS2027: 283</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>• Sharjah-Sat-1 (2023)
 • Sharjah-Sat-2 (2026)</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr"/>
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>4.5 m S-band ground station (SAASST) для серии Sharjah-Sat</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Sharjah Academy for Astronomy, Space Sciences and Technology (SAASST)</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>• Innovative Solutions in Space (ISISpace, Нидерланды) — Sharjah-Sat-2
 • Sharjah Municipality
@@ -1523,26 +1549,26 @@
 • SpaceX (запуски)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AC5" s="5" t="inlineStr">
+      <c r="AD5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Президент (учредитель) университета — Шейх д-р Султан бин Мухаммад аль-Касими, правитель Шарджи; исполнительный глава — канцлер Prof. Esameldin Agamy
 • Тип собственности указан как «эмират Шарджа» (вне стандартного списка) — университет учреждён правителем Шарджи
@@ -1551,7 +1577,7 @@
 • QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sharjah.ac.ae/en/Discover-UoS/Senior-Administration
 • Https://www.sharjah.ac.ae/en/Discover-UoS/Contact-Us
@@ -1562,12 +1588,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1629,80 +1655,85 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>inquiry@aurak.ac.ae</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+971 7 246 8888</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>https://aurak.ac.ae</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Prof. Bassam Alameddine</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>MeznSat (2020)</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>AURAK space lab ground station (used for MeznSat)</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>AURAK Space Lab (School of Engineering)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (MeznSat sponsor/supervisor)
 • Khalifa University (MeznSat partner)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AC6" s="5" t="inlineStr">
+      <c r="AD6" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• THE2027: Reporter (без ранга); в QS2027 топ-500 отсутствует
 • MeznSat (3U, 28.09.2020, Союз/Плесецк) построен 16 студентами AURAK (руководитель Dr. Abdul-Halim Jallad) совместно с Khalifa University под эгидой UAE Space Agency; в nanosats.csv записан на Masdar Institute
@@ -1710,7 +1741,7 @@
 • Сайт защищён капчей — данные получены через WebFetch</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Https://aurak.ac.ae/contact
 • Https://aurak.ac.ae/about/leadership/leadership-team
@@ -1718,12 +1749,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1787,81 +1818,86 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
           <t>ixo@aus.edu</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+971 6 515 5555</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>https://www.aus.edu</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Dr. Tod A. Laursen</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>QS2027: 258</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>Nayif-1 (2017)</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>AUS ground station (UHF, used to operate Nayif-1)</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Mohammed Bin Rashid Space Centre (MBRSC) — Nayif-1 partner and MoU</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Основатель и президент университета — Его Высочество шейх д-р Султан бин Мухаммед Аль-Касими, правитель Шарджи; исполнительный руководитель — канцлер Dr. Tod A. Laursen
 • Nayif-1 (2017) — первый наноспутник ОАЭ, построен студентами AUS совместно с MBRSC и ISIS; наземная станция на кампусе AUS
@@ -1869,7 +1905,7 @@
 • Ixo@aus.edu — International Exchange Office (студенческие обмены); руководитель офиса на сайте не указан (указаны Advisor Grace Morales, Coordinator Lillie De Guzman)</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aus.edu/contact-us
 • Https://www.aus.edu/leadership-cabinet/tod-a-laursen
@@ -1879,12 +1915,12 @@
 • Https://www.mbrsc.ae/satellites/</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1948,74 +1984,79 @@
 Обращение: Dear Professor Piano,</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>nyuad.vc@nyu.edu</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>https://nyuad.nyu.edu</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Prof. Fabio Piano</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Light-1 (2021) — полезная нагрузка RAAD (совместно с Khalifa University)</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>• Center for Astrophysics and Space Science (CASS)
 • PhD program in Astrophysics and Space Systems (с 2025)</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (соглашение 2026 по данным Emirates Mars Mission)
 • Khalifa University
 • National Space Science Agency of Bahrain (Light-1)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AD8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Кампус Нью-Йоркского университета (США); NYUAD не ранжируется QS/THE отдельно (рейтинг у NYU в целом)
 • Prof. Fabio Piano — Vice Chancellor с 06.08.2026 (ранее провост 2010–2020)
@@ -2024,7 +2065,7 @@
 • Американское юрлицо материнского вуза — возможны ограничения экспортного контроля США при космическом сотрудничестве</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Https://nyuad.nyu.edu/en/about/leadership-and-people/office-of-the-vice-chancellor.html
 • Https://nyuad.nyu.edu/en/research/facilities-and-support/participate-in-research-studies/contacts-and-locations.html
@@ -2033,12 +2074,12 @@
 • Https://www.ku.ac.ae/kustil/news</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -2102,72 +2143,77 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>communication@hct.ac.ae</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+971 800 663428 (toll-free 800663428)</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>https://hct.ac.ae</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Dr. Faisal Alayyan</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>President &amp; CEO</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <t>• HCT-SAT 1 (2025)
 • HCT-SAT 2 (2025)</t>
         </is>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>Mohammed Bin Rashid Space Centre (MBRSC)</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="n">
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AC9" s="5" t="inlineStr">
+      <c r="AD9" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Канцлер — H.E. Dr. Ahmad Belhoul Al Falasi (министр спорта ОАЭ); исполнительный глава — President &amp; CEO Dr. Faisal Alayyan
 • HCT-SAT 1/2 — 1U CubeSat, построены студентами HCT совместно с MBRSC (MBRSC — сборка, испытания, запуск и связь). HCT-SAT 1 (Transporter-12, 14.01.2025) — по nanosats.csv сигнала нет; HCT-SAT 2 — 28.11.2025, работает
@@ -2176,7 +2222,7 @@
 • Телефон — бесплатная линия ОАЭ 800 663428 (из-за рубежа может не работать)</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Https://hct.ac.ae/en/about-hct/president-ceos-message/
 • Https://hct.ac.ae/en/about-hct/hct-leadership/
@@ -2186,12 +2232,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -2253,72 +2299,77 @@
 Обращение: Dear Professor Banerjee,</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>office.registrar@dubai.bits-pilani.ac.in</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+971 4 275 3700</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bits-pilani.ac.in/dubai/</t>
-        </is>
-      </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
+          <t>https://www.bits-pilani.ac.in/dubai</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
           <t>Prof. Souri Banerjee</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="inlineStr">
         <is>
           <t>MAHASAT — студенческая программа пикоспутников (2023: испытания 5 пикоспутников на дроне-«носителе», не орбитальные)</t>
         </is>
       </c>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>• Centre for Satellite Communications
 • MAHASAT student pico-satellite programme (рук. Mylswamy Annadurai, экс-директор URSC ISRO)</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="n">
+      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AC10" s="6" t="inlineStr">
+      <c r="AD10" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Кампус индийского BITS Pilani; name_native дан на английском (официальное наименование), арабского официального названия не найдено
 • Директор Prof. Souri Banerjee (назначен в 2024 г., сменил Prof. Srinivasan Madapusi, ныне Pro VC Amity Dubai) — подтверждено Википедией и пресс-релизами, на сайте кампуса имя не найдено
@@ -2327,7 +2378,7 @@
 • Поисковая квота исчерпана — орбитальные запуски MAHASAT после 2023 г. не проверены (в nanosats.csv отсутствуют)</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bits-pilani.ac.in/dubai/
 • Https://en.wikipedia.org/wiki/Birla_Institute_of_Technology_and_Science,_Pilani_%E2%80%93_Dubai_Campus
@@ -2335,12 +2386,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2393,66 +2444,71 @@
       </c>
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr"/>
       <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>https://www.tii.ae</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Dr. Najwa Aaraj</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
+      <c r="X11" s="4" t="inlineStr"/>
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>Abu Dhabi Quantum Optical Ground Station (ADQOGS) — optical/quantum free-space communications</t>
         </is>
       </c>
-      <c r="Y11" s="4" t="inlineStr">
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>Propulsion and Space Research Center (Chief Researcher Dr. Elias Tsoutsanis)</t>
         </is>
       </c>
-      <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="n">
+      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AC11" s="6" t="inlineStr">
+      <c r="AD11" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr"/>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Не университет — исследовательский центр при ATRC (Advanced Technology Research Council) Абу-Даби, включён намеренно
 • E-mail и телефон на сайте не опубликованы (только веб-форма)
 • Космос: собственных спутников нет; в 2026 г. испытан первый в ОАЭ гибридный суборбитальный ракетный двигатель/ракета; оптическая квантовая наземная станция ADQOGS — потенциальный интерес для связи с CubeSat</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tii.ae/contact-us
 • Https://www.tii.ae/about-us
@@ -2460,15 +2516,15 @@
 • Https://www.mediaoffice.abudhabi/en/technology/technology-innovation-institute-launches-abu-dhabi-quantum-optical-ground-station/</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI11"/>
+  <autoFilter ref="A1:AJ11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2479,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI40"/>
+  <dimension ref="A1:AJ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2493,30 +2549,31 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
-    <col width="60" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2577,120 +2634,125 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Стыковка e-mail и адресата</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>E-mail (международный отдел)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>E-mail (общий / ректорат)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Ректор / президент</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг QS</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг THE</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Национальный рейтинг</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -2757,47 +2819,52 @@
 Обращение: Dear Dr. Al Najdawi,</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr"/>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr"/>
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>info@ku.ac.ae</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+971 2 312 3333</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>https://www.ku.ac.ae</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>H.E. Prof. Ebrahim Al Hajri</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr">
+      <c r="S2" s="4" t="inlineStr">
         <is>
           <t>QS2027: 147</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr">
+      <c r="T2" s="4" t="inlineStr">
         <is>
           <t>THE2027: =235</t>
         </is>
       </c>
-      <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>• MYSAT-1 (2018)
 • MeznSat (2020)
@@ -2805,17 +2872,17 @@
 • Light-1 (2021)</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>6U CubeSat с собственной экологичной HTP-двигательной установкой (совместно с UAE Space Agency, запуск ожидался к концу 2026)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>Наземная станция KU Space Technology and Innovation Lab (указана на странице facilities; параметры не раскрыты)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>• Khalifa University Space Technology and Innovation Center (KUSTIC)
 • Khalifa University Space Technology and Innovation Lab (KUSTIL)
@@ -2823,7 +2890,7 @@
 • Thermal vacuum chamber &amp; cleanroom</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency
 • Yahsat (Al Yah Satellite Communications)
@@ -2833,26 +2900,26 @@
 • American University of Ras Al Khaimah (MeznSat)</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AD2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Председатель Попечительского совета — Шейх Хамед бин Заед Аль Нахайян (H.H. Sheikh Hamed bin Zayed Al Nahyan); исполнительный глава — президент Prof. Ebrahim Al Hajri
 • Отдельный e-mail международного офиса не опубликован; isso@ku.ac.ae и studyabroad@ku.ac.ae — студенческие службы. Для партнёрства — info@ku.ac.ae; профильный руководитель — Dr. Ashraf Al Najdawi, Vice President, External Relations
@@ -2861,7 +2928,7 @@
 • QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ku.ac.ae/university-leadership
 • Https://www.ku.ac.ae/contact-us
@@ -2872,12 +2939,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2929,35 +2996,40 @@
       </c>
       <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M3" s="4" t="inlineStr"/>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+971 4 607 1200</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>https://www.mbrsc.ae</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>H.E. Salem Humaid AlMarri</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>Director General</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>• DubaiSat-1 (2009)
 • DubaiSat-2 (2013)
@@ -2973,19 +3045,19 @@
 • HCT-SAT 2 (2025)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• PHI-2…PHI-5 (12U, Payload Hosting Initiative, with NanoAvionics)
 • Emirates Airlock for NASA Lunar Gateway
 • Rashid rover programme</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>MBRSC ground station (Al Khawaneej, Dubai) — offers ground station services</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• Satellite Development Programme
 • UAE Astronaut Programme
@@ -2993,7 +3065,7 @@
 • Payload Hosting Initiative (PHI)</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• UNOOSA (PHI, 'Access to Space for All')
 • NASA (astronaut training, Lunar Gateway Emirates Airlock)
@@ -3003,22 +3075,22 @@
 • Satrec Initiative (DubaiSat, Etihad-SAT)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr"/>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr"/>
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Не университет, а государственное космическое агентство эмирата Дубай (включено намеренно); председатель — H.E. Hamad Obaid Al Mansoori
 • E-mail на официальном сайте не опубликован; сторонние источники (Bayut и др.) указывают info@mbrsc.ae — не проверено на официальной странице
@@ -3026,7 +3098,7 @@
 • Etihad-SAT: на сайте MBRSC указан запуск в марте 2025; HCT-SAT 2 и PHI-Demo — по nanosats.csv; Hope Probe — марсианский орбитальный аппарат (не CubeSat)</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mbrsc.ae/contact-us/
 • Https://www.mbrsc.ae/about/
@@ -3036,12 +3108,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -3104,94 +3176,99 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>servicedesk@uaeu.ac.ae</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+971 3 701 7111</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>https://www.uaeu.ac.ae</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Ali Alraeesi</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr">
         <is>
           <t>QS2027: 217</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>THE2027: =235</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr">
         <is>
           <t>• ALainSat-1 (2025)
 • LEONAV-1 (2026)</t>
         </is>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>813 Satellite (Arab Satellite 813, EO, Arab cooperation project)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>NSSTC Ground Segment at UAEU (Al Ain): S/X-band dish antennas + UHF antenna</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>National Space Science and Technology Center (NSSTC)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (NSSTC co-founder)
 • Telecommunications and Digital Government Regulatory Authority (ICT Fund, NSSTC co-founder)
 • IEEE GRSS (AlAinSat-1 payloads)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AC4" s="5" t="inlineStr">
+      <c r="AD4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Канцлер (Chancellor) — H.E. Zaki Anwar Nusseibeh; исполнительный руководитель — вице-канцлер Prof. Ahmed Ali Alraeesi
 • Отдельный e-mail международного офиса на сайте не найден; servicedesk@uaeu.ac.ae — общий сервис-деск. Для космической тематики лучше параллельно писать в NSSTC: nsstc@uaeu.ac.ae
@@ -3199,7 +3276,7 @@
 • MeznSat (2020) построен Khalifa University и AURAK, не UAEU</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uaeu.ac.ae/en/contact/index.shtml
 • Https://www.uaeu.ac.ae/en/vc/index.shtml
@@ -3211,12 +3288,12 @@
 • Https://www.emirates247.com/uae/uaeu-announces-successful-launch-of-leonav-1-satellite/3485</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3282,66 +3359,71 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>OIR@sharjah.ac.ae</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>info@sharjah.ac.ae</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+971 6 558 5000</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>https://www.sharjah.ac.ae</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Prof. Esameldin Agamy</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>QS2027: 283</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr">
         <is>
           <t>• Sharjah-Sat-1 (2023)
 • Sharjah-Sat-2 (2026)</t>
         </is>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr"/>
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>4.5 m S-band ground station (SAASST) для серии Sharjah-Sat</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>Sharjah Academy for Astronomy, Space Sciences and Technology (SAASST)</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>• Innovative Solutions in Space (ISISpace, Нидерланды) — Sharjah-Sat-2
 • Sharjah Municipality
@@ -3350,26 +3432,26 @@
 • SpaceX (запуски)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AC5" s="5" t="inlineStr">
+      <c r="AD5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Президент (учредитель) университета — Шейх д-р Султан бин Мухаммад аль-Касими, правитель Шарджи; исполнительный глава — канцлер Prof. Esameldin Agamy
 • Тип собственности указан как «эмират Шарджа» (вне стандартного списка) — университет учреждён правителем Шарджи
@@ -3378,7 +3460,7 @@
 • QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sharjah.ac.ae/en/Discover-UoS/Senior-Administration
 • Https://www.sharjah.ac.ae/en/Discover-UoS/Contact-Us
@@ -3389,12 +3471,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3456,80 +3538,85 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr"/>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>inquiry@aurak.ac.ae</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+971 7 246 8888</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>https://aurak.ac.ae</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Prof. Bassam Alameddine</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="4" t="inlineStr"/>
       <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr">
         <is>
           <t>MeznSat (2020)</t>
         </is>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>AURAK space lab ground station (used for MeznSat)</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>AURAK Space Lab (School of Engineering)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (MeznSat sponsor/supervisor)
 • Khalifa University (MeznSat partner)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AC6" s="5" t="inlineStr">
+      <c r="AD6" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• THE2027: Reporter (без ранга); в QS2027 топ-500 отсутствует
 • MeznSat (3U, 28.09.2020, Союз/Плесецк) построен 16 студентами AURAK (руководитель Dr. Abdul-Halim Jallad) совместно с Khalifa University под эгидой UAE Space Agency; в nanosats.csv записан на Masdar Institute
@@ -3537,7 +3624,7 @@
 • Сайт защищён капчей — данные получены через WebFetch</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Https://aurak.ac.ae/contact
 • Https://aurak.ac.ae/about/leadership/leadership-team
@@ -3545,12 +3632,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3614,81 +3701,86 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
           <t>ixo@aus.edu</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+971 6 515 5555</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>https://www.aus.edu</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Dr. Tod A. Laursen</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>QS2027: 258</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr">
         <is>
           <t>Nayif-1 (2017)</t>
         </is>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>AUS ground station (UHF, used to operate Nayif-1)</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Mohammed Bin Rashid Space Centre (MBRSC) — Nayif-1 partner and MoU</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Основатель и президент университета — Его Высочество шейх д-р Султан бин Мухаммед Аль-Касими, правитель Шарджи; исполнительный руководитель — канцлер Dr. Tod A. Laursen
 • Nayif-1 (2017) — первый наноспутник ОАЭ, построен студентами AUS совместно с MBRSC и ISIS; наземная станция на кампусе AUS
@@ -3696,7 +3788,7 @@
 • Ixo@aus.edu — International Exchange Office (студенческие обмены); руководитель офиса на сайте не указан (указаны Advisor Grace Morales, Coordinator Lillie De Guzman)</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aus.edu/contact-us
 • Https://www.aus.edu/leadership-cabinet/tod-a-laursen
@@ -3706,12 +3798,12 @@
 • Https://www.mbrsc.ae/satellites/</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3775,74 +3867,79 @@
 Обращение: Dear Professor Piano,</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>nyuad.vc@nyu.edu</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>https://nyuad.nyu.edu</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Prof. Fabio Piano</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="V8" s="4" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr">
         <is>
           <t>Light-1 (2021) — полезная нагрузка RAAD (совместно с Khalifa University)</t>
         </is>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>• Center for Astrophysics and Space Science (CASS)
 • PhD program in Astrophysics and Space Systems (с 2025)</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (соглашение 2026 по данным Emirates Mars Mission)
 • Khalifa University
 • National Space Science Agency of Bahrain (Light-1)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AD8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Кампус Нью-Йоркского университета (США); NYUAD не ранжируется QS/THE отдельно (рейтинг у NYU в целом)
 • Prof. Fabio Piano — Vice Chancellor с 06.08.2026 (ранее провост 2010–2020)
@@ -3851,7 +3948,7 @@
 • Американское юрлицо материнского вуза — возможны ограничения экспортного контроля США при космическом сотрудничестве</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Https://nyuad.nyu.edu/en/about/leadership-and-people/office-of-the-vice-chancellor.html
 • Https://nyuad.nyu.edu/en/research/facilities-and-support/participate-in-research-studies/contacts-and-locations.html
@@ -3860,12 +3957,12 @@
 • Https://www.ku.ac.ae/kustil/news</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3929,72 +4026,77 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>communication@hct.ac.ae</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+971 800 663428 (toll-free 800663428)</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>https://hct.ac.ae</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Dr. Faisal Alayyan</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>President &amp; CEO</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="4" t="inlineStr"/>
       <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr">
         <is>
           <t>• HCT-SAT 1 (2025)
 • HCT-SAT 2 (2025)</t>
         </is>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>Mohammed Bin Rashid Space Centre (MBRSC)</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="n">
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AC9" s="5" t="inlineStr">
+      <c r="AD9" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Канцлер — H.E. Dr. Ahmad Belhoul Al Falasi (министр спорта ОАЭ); исполнительный глава — President &amp; CEO Dr. Faisal Alayyan
 • HCT-SAT 1/2 — 1U CubeSat, построены студентами HCT совместно с MBRSC (MBRSC — сборка, испытания, запуск и связь). HCT-SAT 1 (Transporter-12, 14.01.2025) — по nanosats.csv сигнала нет; HCT-SAT 2 — 28.11.2025, работает
@@ -4003,7 +4105,7 @@
 • Телефон — бесплатная линия ОАЭ 800 663428 (из-за рубежа может не работать)</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Https://hct.ac.ae/en/about-hct/president-ceos-message/
 • Https://hct.ac.ae/en/about-hct/hct-leadership/
@@ -4013,12 +4115,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -4080,72 +4182,77 @@
 Обращение: Dear Professor Banerjee,</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>office.registrar@dubai.bits-pilani.ac.in</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+971 4 275 3700</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bits-pilani.ac.in/dubai/</t>
-        </is>
-      </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
+          <t>https://www.bits-pilani.ac.in/dubai</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
           <t>Prof. Souri Banerjee</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="4" t="inlineStr"/>
       <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="inlineStr">
         <is>
           <t>MAHASAT — студенческая программа пикоспутников (2023: испытания 5 пикоспутников на дроне-«носителе», не орбитальные)</t>
         </is>
       </c>
-      <c r="X10" s="4" t="inlineStr"/>
-      <c r="Y10" s="4" t="inlineStr">
+      <c r="Y10" s="4" t="inlineStr"/>
+      <c r="Z10" s="4" t="inlineStr">
         <is>
           <t>• Centre for Satellite Communications
 • MAHASAT student pico-satellite programme (рук. Mylswamy Annadurai, экс-директор URSC ISRO)</t>
         </is>
       </c>
-      <c r="Z10" s="4" t="inlineStr"/>
       <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="n">
+      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AC10" s="6" t="inlineStr">
+      <c r="AD10" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Кампус индийского BITS Pilani; name_native дан на английском (официальное наименование), арабского официального названия не найдено
 • Директор Prof. Souri Banerjee (назначен в 2024 г., сменил Prof. Srinivasan Madapusi, ныне Pro VC Amity Dubai) — подтверждено Википедией и пресс-релизами, на сайте кампуса имя не найдено
@@ -4154,7 +4261,7 @@
 • Поисковая квота исчерпана — орбитальные запуски MAHASAT после 2023 г. не проверены (в nanosats.csv отсутствуют)</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bits-pilani.ac.in/dubai/
 • Https://en.wikipedia.org/wiki/Birla_Institute_of_Technology_and_Science,_Pilani_%E2%80%93_Dubai_Campus
@@ -4162,12 +4269,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -4220,66 +4327,71 @@
       </c>
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M11" s="4" t="inlineStr"/>
       <c r="N11" s="4" t="inlineStr"/>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>https://www.tii.ae</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Dr. Najwa Aaraj</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="4" t="inlineStr"/>
       <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
+      <c r="X11" s="4" t="inlineStr"/>
+      <c r="Y11" s="4" t="inlineStr">
         <is>
           <t>Abu Dhabi Quantum Optical Ground Station (ADQOGS) — optical/quantum free-space communications</t>
         </is>
       </c>
-      <c r="Y11" s="4" t="inlineStr">
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>Propulsion and Space Research Center (Chief Researcher Dr. Elias Tsoutsanis)</t>
         </is>
       </c>
-      <c r="Z11" s="4" t="inlineStr"/>
       <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="n">
+      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AC11" s="6" t="inlineStr">
+      <c r="AD11" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr"/>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Не университет — исследовательский центр при ATRC (Advanced Technology Research Council) Абу-Даби, включён намеренно
 • E-mail и телефон на сайте не опубликованы (только веб-форма)
 • Космос: собственных спутников нет; в 2026 г. испытан первый в ОАЭ гибридный суборбитальный ракетный двигатель/ракета; оптическая квантовая наземная станция ADQOGS — потенциальный интерес для связи с CubeSat</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tii.ae/contact-us
 • Https://www.tii.ae/about-us
@@ -4287,12 +4399,12 @@
 • Https://www.mediaoffice.abudhabi/en/technology/technology-innovation-institute-launches-abu-dhabi-quantum-optical-ground-station/</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4345,63 +4457,68 @@
       </c>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M12" s="4" t="inlineStr"/>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>+971 2 501 5717</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>https://www.adu.ac.ae</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Prof. Ghassan Aouad</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>QS2027: 348</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="4" t="inlineStr"/>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="n">
+      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="7" t="inlineStr">
+      <c r="AD12" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr"/>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Сайт adu.ac.ae рендерится JavaScript — контакты сняты с WSCUC (аккредитатор) и поисковой выдачи
 • По поисковой выдаче: международный офис intl.office@adu.ac.ae, тел. +971 2 501 5555 (на открытой странице не подтверждено)
@@ -4411,19 +4528,19 @@
 • QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wscuc.org/institutions/abu-dhabi-university/
 • Https://www.mediaoffice.abudhabi/en/education/hamdan-bin-zayed-chairs-1st-abu-dhabi-university-board-of-trustees-meeting-in-2026/
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4486,77 +4603,82 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>inquiry@ajman.ac.ae</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>+971 6 748 2222</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>https://www.ajman.ac.ae</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Dr. Karim Seghir</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>QS2027: 397</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>THE2027: 376–400</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="4" t="inlineStr"/>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="n">
+      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="7" t="inlineStr">
+      <c r="AD13" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>• Есть Office of International Academic Affairs (OIAA, oiaa.ajman.ac.ae); директор — Victoria Joy Winter (Director of International Academic Affairs, по справочнику сотрудников), e-mail офиса на сайте не опубликован
 • Космических проектов/спутников не найдено (поиск + nanosats.csv)</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ajman.ac.ae/en/contact-us
 • Https://www.ajman.ac.ae/en/about/message-from-the-chancellor
@@ -4564,12 +4686,12 @@
 • Https://oiaa.ajman.ac.ae/en/</t>
         </is>
       </c>
-      <c r="AH13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4622,63 +4744,68 @@
       </c>
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M14" s="4" t="inlineStr"/>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>+971 3 702 4888</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>https://aau.ac.ae</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Prof. Amer Mohammad Jaser Qasem</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>QS2027: 559</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>THE2027: 401–450</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="n">
+      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC14" s="7" t="inlineStr">
+      <c r="AD14" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr"/>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AE14" s="4" t="inlineStr"/>
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail и e-mail международного офиса на сайте не опубликованы (только формы); формат адресов сотрудников — имя.фамилия@aau.ac.ae
 • Не путать со спутником Al Ain Sat-1 (AlAinSat-1) — это проект UAE University (NSSTC), а не Al Ain University
@@ -4687,7 +4814,7 @@
 • QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>• Https://aau.ac.ae/en/contact-us
 • Https://aau.ac.ae/en/about-aau/senior-management
@@ -4695,12 +4822,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4763,67 +4890,72 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>eau.info@emirates.com</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>+971 4 605 0100</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>https://www.eau.ac.ae</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmad Al Ali</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr"/>
       <c r="S15" s="4" t="inlineStr"/>
       <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="n">
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr">
+      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr">
         <is>
           <t>Department of Aerospace Engineering</t>
         </is>
       </c>
-      <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="n">
+      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="8" t="inlineStr">
+      <c r="AD15" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="inlineStr">
+      <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>• Университет принадлежит Emirates Group (государственная группа Дубая); канцлер — шейх Ахмед бин Саид Аль Мактум (председатель Emirates Airline &amp; Group); исполнительный руководитель — вице-канцлер Prof. Ahmad Al Ali
 • Общий адрес почты на домене emirates.com (eau.info@emirates.com); международный офис на сайте не найден
@@ -4831,19 +4963,19 @@
 • Сайт динамический — страницы руководства не читаются автоматически; руководство подтверждено через Dubai Media Office (июль 2025)</t>
         </is>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AH15" s="4" t="inlineStr">
         <is>
           <t>• Https://www.eau.ac.ae/contact-us
 • Https://mediaoffice.ae/en/news/2025/july/01-07/emirates-aviation-university-marks-35-years
 • Https://ieeexplore.ieee.org/document/5966842/</t>
         </is>
       </c>
-      <c r="AH15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4908,69 +5040,74 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
           <t>engagement@cud.ac.ae</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>info@cud.ac.ae</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+971 4 321 1991</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>https://www.cud.ac.ae</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>Prof. Karim Chelli</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>President &amp; Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>QS2027: 616</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr"/>
       <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="inlineStr"/>
       <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="n">
+      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC16" s="7" t="inlineStr">
+      <c r="AD16" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD16" s="4" t="inlineStr">
+      <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>• Engagement@cud.ac.ae — ящик Community Outreach Office для новых коллабораций (тел. +971 4 709 6145); отдельного международного офиса нет
 • Руководитель Community Outreach Office поимённо не указан
@@ -4978,7 +5115,7 @@
 • QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
         </is>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AH16" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cud.ac.ae/contact
 • Https://www.cud.ac.ae/about/senior-management
@@ -4986,12 +5123,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH16" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -5057,73 +5194,78 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
           <t>oeir@ud.ac.ae</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>info@ud.ac.ae</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+971 4 556 6800</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>https://ud.ac.ae</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Dr. Eesa Al Bastaki</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>QS2027: 781–790</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>THE2027: Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="inlineStr"/>
       <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="n">
+      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC17" s="7" t="inlineStr">
+      <c r="AD17" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD17" s="4" t="inlineStr">
+      <c r="AE17" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>• Связан с Dubai Chamber; президент Dr. Eesa Al Bastaki — инженер связи, бывший профессор UAEU, почётный председатель IEEE (UAE)
 • Руководитель офиса EIR поимённо не указан; на странице EIR приведены обращения президента и провоста (Prof. Hussain Al Ahmad)
@@ -5132,7 +5274,7 @@
 • QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
         </is>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>• Https://ud.ac.ae/leadership/
 • Https://ud.ac.ae/about-us/external-and-international-relations-eir/
@@ -5140,12 +5282,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -5208,67 +5350,72 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>info@zu.ac.ae</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+971 2 599 3111</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>https://www.zu.ac.ae</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Dr. Kevin Hall</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>President &amp; CEO</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr">
+      <c r="S18" s="4" t="inlineStr"/>
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="4" t="inlineStr"/>
       <c r="Z18" s="4" t="inlineStr"/>
       <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="n">
+      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC18" s="7" t="inlineStr">
+      <c r="AD18" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD18" s="4" t="inlineStr">
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>• Два кампуса: Абу-Даби и Дубай (тел. Дубай +971 4 402 1111)
 • Dr. Kevin Hall назначен President &amp; CEO с 01.11.2025 (бывший президент University of Victoria); председатель совета попечителей — Shamma bint Sohail Al Mazrui (по данным поиска)
@@ -5276,19 +5423,19 @@
 • Международный офис на сайте не найден; спутников не найдено</t>
         </is>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AH18" s="4" t="inlineStr">
         <is>
           <t>• Https://www.zu.ac.ae/main/en/contact_us/index
 • Https://cheknews.ca/former-uvic-president-kevin-hall-named-ceo-of-university-in-dubai-abu-dhabi-1282755/
 • Https://x.com/Zayed_U/status/1975551341188554950</t>
         </is>
       </c>
-      <c r="AH18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="inlineStr"/>
+      <c r="AI18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -5352,67 +5499,72 @@
 Обращение: Dear Professor Venkatramana,</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>chancellor@gmu.ac.ae</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+971 6 743 1333</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>https://gmu.ac.ae</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Prof. Manda Venkatramana</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="inlineStr"/>
       <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="n">
+      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC19" s="7" t="inlineStr">
+      <c r="AD19" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD19" s="4" t="inlineStr">
+      <c r="AE19" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>• Частный медицинский университет группы Thumbay (Thumbay Group)
 • Отдельного e-mail международного офиса нет; есть страница «Regional and International Partners». Использован e-mail офиса канцлера
@@ -5421,7 +5573,7 @@
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
         </is>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>• Https://gmu.ac.ae/contact-us/
 • Https://gmu.ac.ae/aboutgmu/office-of-the-chancellor/
@@ -5429,12 +5581,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="inlineStr"/>
+      <c r="AI19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -5482,51 +5634,56 @@
       <c r="I20" s="4" t="inlineStr"/>
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M20" s="4" t="inlineStr"/>
       <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>https://www.alqasimia.ac.ae</t>
         </is>
       </c>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Prof. Awad Husain AlKhalaf</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr"/>
       <c r="S20" s="4" t="inlineStr"/>
       <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="inlineStr"/>
       <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="n">
+      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC20" s="7" t="inlineStr">
+      <c r="AD20" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD20" s="4" t="inlineStr"/>
-      <c r="AE20" s="4" t="inlineStr">
+      <c r="AE20" s="4" t="inlineStr"/>
+      <c r="AF20" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Учреждена правителем Шарджи (шейх Султан бин Мухаммад аль-Касими) — тип собственности «эмират Шарджа» вне стандартного списка, проверить
 • Сайт (SharePoint) не публикует адрес/телефон/e-mail в доступном HTML; контакты не найдены, поисковая квота исчерпана
@@ -5536,7 +5693,7 @@
 • Перепроверка: Канцлер подтверждён на странице попечительского совета (без даты); контакты на сайте по-прежнему не опубликованы — уровень low сохранён</t>
         </is>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
+      <c r="AH20" s="4" t="inlineStr">
         <is>
           <t>• Https://www.alqasimia.ac.ae/en/AboutAQU/Pages/UniversityChancellor.aspx
 • Https://www.alqasimia.ac.ae/en
@@ -5544,12 +5701,12 @@
 • Https://www.alqasimia.ac.ae/en/AboutAQU/Pages/BOT.aspx</t>
         </is>
       </c>
-      <c r="AH20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI20" s="4" t="inlineStr"/>
+      <c r="AI20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -5612,81 +5769,86 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>info@aud.edu</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>+971 4 399 9000</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>https://www.aud.edu</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Dr. Kyle Long</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr"/>
       <c r="S21" s="4" t="inlineStr"/>
       <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="inlineStr"/>
       <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="n">
+      <c r="AB21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" s="7" t="inlineStr">
+      <c r="AD21" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>• THE2027: Reporter (без ранга)
 • На сайте есть раздел International Mobility Opportunities, но отдельного e-mail международного офиса нет
 • Спутников не найдено</t>
         </is>
       </c>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aud.edu/get-in-touch/
 • Https://www.aud.edu/university-overview/aud-leadership/office-of-the-president/</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr"/>
+      <c r="AI21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -5750,63 +5912,68 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>info@aue.ae</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr"/>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>https://aue.ae</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Prof. Muthanna G. Abdul Razzaq</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>President &amp; CEO</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr">
+      <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr">
         <is>
           <t>THE2027: Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="n">
+      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC22" s="7" t="inlineStr">
+      <c r="AD22" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD22" s="4" t="inlineStr">
+      <c r="AE22" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>• Сайт aue.ae блокирует автоматический доступ (403) — данные из Википедии и каталога emiratesuniversities.org; требуется ручная проверка
 • THE2027: в статусе Reporter (не ранжирован)
@@ -5817,19 +5984,19 @@
 • Перепроверка: 04.10.2026: aue.ae по-прежнему 403; президент Prof. Muthanna G. Abdul Razzaq подтверждается только поиском — данные не изменены</t>
         </is>
       </c>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AH22" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/American_University_in_the_Emirates
 • Https://emiratesuniversities.org/listing/american-emirates/
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH22" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI22" s="4" t="inlineStr"/>
+      <c r="AI22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -5892,63 +6059,68 @@
 Обращение: Dear Professor Srinivasan,</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr"/>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>info@amityuniversity.ae</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>+971 4 455 4900</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>https://amityuniversity.ae</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Dr. Saif Al Seiari</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="R23" s="4" t="inlineStr">
         <is>
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="R23" s="4" t="inlineStr"/>
       <c r="S23" s="4" t="inlineStr"/>
       <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="n">
+      <c r="U23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="n">
+      <c r="AB23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC23" s="7" t="inlineStr">
+      <c r="AD23" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD23" s="4" t="inlineStr">
+      <c r="AE23" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• Кампус индийской Amity University; в UAE лицензирован CAA
 • Есть бакалавриат Aerospace Engineering (B.Tech/BSc) — релевантная база для CubeSat-сотрудничества
@@ -5957,7 +6129,7 @@
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AH23" s="4" t="inlineStr">
         <is>
           <t>• Https://amityuniversity.ae/contact-us
 • Https://amityuniversity.ae/about-amity/leadership-team/senior-leadership
@@ -5966,12 +6138,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -6030,63 +6202,68 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>info@cu.ac.ae</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>+971 6 711 0000</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>https://cu.ac.ae</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>Mr. Imran Khan</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr"/>
       <c r="S24" s="4" t="inlineStr"/>
       <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="n">
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="n">
+      <c r="AB24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC24" s="7" t="inlineStr">
+      <c r="AD24" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD24" s="4" t="inlineStr">
+      <c r="AE24" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• THE2027: Reporter (без ранга)
 • Председатель совета попечителей — шейх Рашид бин Хумаид Аль Нуайми; президент — Mr. Imran Khan (без учёной степени на сайте)
@@ -6094,18 +6271,18 @@
 • Космической активности нет; nanosats.csv (UAE): записей нет</t>
         </is>
       </c>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AH24" s="4" t="inlineStr">
         <is>
           <t>• Https://cu.ac.ae/contact-us/
 • Https://cu.ac.ae/about-us/</t>
         </is>
       </c>
-      <c r="AH24" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -6169,59 +6346,64 @@
 Обращение: Dear Professor Khalifa,</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>info@dmu.ae</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>800 DMU1 (8003681, UAE toll-free)</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>https://dmu.ae</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr"/>
       <c r="Q25" s="4" t="inlineStr"/>
       <c r="R25" s="4" t="inlineStr"/>
-      <c r="S25" s="4" t="inlineStr">
+      <c r="S25" s="4" t="inlineStr"/>
+      <c r="T25" s="4" t="inlineStr">
         <is>
           <t>THE2027: Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="n">
+      <c r="U25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="n">
+      <c r="AB25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC25" s="7" t="inlineStr">
+      <c r="AD25" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD25" s="4" t="inlineStr">
+      <c r="AE25" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>• Бывший Dubai Medical College for Girls; официальный сайт — dmu.ae (НЕ dmu.ac.ae — это De Montfort University Dubai)
 • Исполнительный глава (канцлер/президент) на сайте не найден; Vice Chancellor – Academic Affairs: Prof. Sherief Khalifa. По Википедии: председатель — Saeed Bin Ahmed Al Lootah, декан — Prof. Mohammed Galal El Din
@@ -6231,7 +6413,7 @@
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
         </is>
       </c>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>• Https://dmu.ae/home/contact-us/
 • Https://dmu.ae/home/vca-message/
@@ -6240,12 +6422,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH25" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI25" s="4" t="inlineStr"/>
+      <c r="AI25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -6308,63 +6490,68 @@
 Обращение: Dear Dr. Al Taee,</t>
         </is>
       </c>
-      <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>info@ecae.ac.ae</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>+971 2 509 9888</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>https://www.ecae.ac.ae</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>Dr. May Laith Al Taee</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
+      <c r="R26" s="4" t="inlineStr">
         <is>
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="R26" s="4" t="inlineStr"/>
       <c r="S26" s="4" t="inlineStr"/>
       <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="n">
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="n">
+      <c r="AB26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC26" s="7" t="inlineStr">
+      <c r="AD26" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD26" s="4" t="inlineStr">
+      <c r="AE26" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>• Сайт ecae.ac.ae напрямую из нашей сети недоступен; страницы (главная, About us, Contact us) открыты через r.jina.ai 04.10.2026. Кампусы также в Аль-Айне и Аджмане (здания Teacher Training Institution Минобразования)
 • Председатель совета (по Википедии) — H.E. Sarah Yousef Al Amiri — на открытых страницах не проверено. Отдельный международный офис и его e-mail на сайте не найдены
@@ -6374,18 +6561,18 @@
 • Перепроверка: Сайт ecae.ac.ae открыт через reader-сервис 04.10.2026: Vice Chancellor Dr. May Laith Al Taee, info@ecae.ac.ae, тел. +971 2 509 9888 и адрес кампуса (Khalifa City, Абу-Даби) подтверждены; дата страницы руководства не указана</t>
         </is>
       </c>
-      <c r="AG26" s="4" t="inlineStr">
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Emirates_College_for_Advanced_Education
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH26" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="inlineStr"/>
+      <c r="AI26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6448,55 +6635,60 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>info@fchs.ac.ae</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>+971 2 507 8765</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>https://www.fchs.ac.ae</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr"/>
       <c r="Q27" s="4" t="inlineStr"/>
       <c r="R27" s="4" t="inlineStr"/>
       <c r="S27" s="4" t="inlineStr"/>
       <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="n">
+      <c r="U27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="n">
+      <c r="AB27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC27" s="7" t="inlineStr">
+      <c r="AD27" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD27" s="4" t="inlineStr">
+      <c r="AE27" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• Учреждён в 2006 г. в системе ACTVET (Abu Dhabi Centre for Technical and Vocational Education and Training)
 • Кампусы (официальный сайт): Абу-Даби (Al Mafraq, +971 2 507 8765, info@fchs.ac.ae), Эль-Айн (Al Maqam, +971 3 703 5555, alain@fchs.ac.ae), Аль-Дафра (Madinat Zayed, +971 2 898 6915, aldhafra@fchs.ac.ae), Аджман (+971 6 701 7200, ajman@fchs.ac.ae)
@@ -6505,19 +6697,19 @@
 • Перепроверка: Общий e-mail info@fchs.ac.ae, телефон и кампусы подтверждены через официальный API сайта fchs.ac.ae (обновл. 06.2026); руководитель не найден</t>
         </is>
       </c>
-      <c r="AG27" s="4" t="inlineStr">
+      <c r="AH27" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fchs.ac.ae/contact-us
 • Https://www.fchs.ac.ae/
 • Https://www.fchs.ac.ae/api/campuses</t>
         </is>
       </c>
-      <c r="AH27" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI27" s="4" t="inlineStr"/>
+      <c r="AI27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6570,55 +6762,60 @@
       </c>
       <c r="J28" s="4" t="inlineStr"/>
       <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M28" s="4" t="inlineStr"/>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>+971 4 571 7000</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>https://www.hw.ac.uk/dubai</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>Prof. Dame Heather McGregor</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="R28" s="4" t="inlineStr">
         <is>
           <t>Provost and Vice-Principal (Dubai)</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr"/>
       <c r="S28" s="4" t="inlineStr"/>
       <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="n">
+      <c r="U28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="n">
+      <c r="AB28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC28" s="7" t="inlineStr">
+      <c r="AD28" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD28" s="4" t="inlineStr"/>
-      <c r="AE28" s="4" t="inlineStr">
+      <c r="AE28" s="4" t="inlineStr"/>
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>• Кампус британского Heriot-Watt University (Эдинбург); в рейтингах QS/THE учитывается в составе головного вуза (Великобритания), отдельно не ранжируется
 • Общий e-mail на сайте не опубликован (только формы) — рекомендуется обращение через Provost
@@ -6627,19 +6824,19 @@
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
         </is>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
+      <c r="AH28" s="4" t="inlineStr">
         <is>
           <t>• Https://www.hw.ac.uk/dubai/about
 • Https://www.hw.ac.uk/dubai/about/provost-and-vice-principal
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH28" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI28" s="4" t="inlineStr"/>
+      <c r="AI28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6691,51 +6888,56 @@
       </c>
       <c r="J29" s="4" t="inlineStr"/>
       <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M29" s="4" t="inlineStr"/>
       <c r="N29" s="4" t="inlineStr"/>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr"/>
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>https://lu.ac.ae</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohamed Mahjoub Dhiaf</t>
         </is>
       </c>
-      <c r="Q29" s="4" t="inlineStr">
+      <c r="R29" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R29" s="4" t="inlineStr"/>
       <c r="S29" s="4" t="inlineStr"/>
       <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="n">
+      <c r="U29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="n">
+      <c r="AB29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC29" s="7" t="inlineStr">
+      <c r="AD29" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD29" s="4" t="inlineStr"/>
-      <c r="AE29" s="4" t="inlineStr">
+      <c r="AE29" s="4" t="inlineStr"/>
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>• Кампусы в Абу-Даби и Эль-Айне (новый кампус в Эль-Айне открыт в 2025)
 • Main_fields — ориентировочно, не проверены по сайту
@@ -6744,17 +6946,17 @@
 • Перепроверка: Сайт закрыт Cloudflare; по поисковому индексу официальных страниц уточнены полное имя президента и адрес; e-mail не подтверждён</t>
         </is>
       </c>
-      <c r="AG29" s="4" t="inlineStr">
+      <c r="AH29" s="4" t="inlineStr">
         <is>
           <t>Https://www.education-uae.com/liwa-university-al-ain-campus-launch/</t>
         </is>
       </c>
-      <c r="AH29" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI29" s="4" t="inlineStr"/>
+      <c r="AI29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6818,63 +7020,68 @@
 Обращение: Dear Dr. Sudhindra,</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>info@manipaldubai.com</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>+971 4 429 0888</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>https://www.manipaldubai.com</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Dr. S. Sudhindra</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
+      <c r="R30" s="4" t="inlineStr">
         <is>
           <t>Pro Vice Chancellor – MAHE Dubai</t>
         </is>
       </c>
-      <c r="R30" s="4" t="inlineStr"/>
       <c r="S30" s="4" t="inlineStr"/>
       <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="n">
+      <c r="U30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
-      <c r="AB30" s="4" t="n">
+      <c r="AB30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC30" s="7" t="inlineStr">
+      <c r="AD30" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD30" s="4" t="inlineStr">
+      <c r="AE30" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>• Кампус индийской Manipal Academy of Higher Education (MAHE); Vice Chancellor MAHE — Dr. Sharath Kumar Rao K (Индия)
 • Сайт прямо указывает: по академическим/институциональным вопросам обращаться к Dr. Sudhindra — sudhindra.shamanna@manipaldubai.com
@@ -6883,7 +7090,7 @@
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
         </is>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
+      <c r="AH30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.manipaldubai.com/
 • Https://www.manipaldubai.com/contact-us
@@ -6892,12 +7099,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI30" s="4" t="inlineStr"/>
+      <c r="AI30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -6960,80 +7167,85 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>info@mdx.ac.ae</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>+971 4 367 8100</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>https://www.mdx.ac.ae</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Prof. Cedwyn Fernandes</t>
         </is>
       </c>
-      <c r="Q31" s="4" t="inlineStr">
+      <c r="R31" s="4" t="inlineStr">
         <is>
           <t>Provost and Director</t>
         </is>
       </c>
-      <c r="R31" s="4" t="inlineStr"/>
       <c r="S31" s="4" t="inlineStr"/>
       <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="n">
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
-      <c r="AB31" s="4" t="n">
+      <c r="AB31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC31" s="7" t="inlineStr">
+      <c r="AD31" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD31" s="4" t="inlineStr">
+      <c r="AE31" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>• Кампус британского Middlesex University (Лондон); партнёрские решения могут требовать согласования с головным вузом
 • Main_fields — ориентировочно; nanosats.csv (UAE): записей нет</t>
         </is>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
+      <c r="AH31" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mdx.ac.ae/contact-us
 • Https://www.mdx.ac.ae/about-us/our-people</t>
         </is>
       </c>
-      <c r="AH31" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI31" s="4" t="inlineStr"/>
+      <c r="AI31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -7086,51 +7298,56 @@
       </c>
       <c r="J32" s="4" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M32" s="4" t="inlineStr"/>
       <c r="N32" s="4" t="inlineStr"/>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>https://mbzuai.ac.ae</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>Prof. Eric Xing</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="R32" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R32" s="4" t="inlineStr"/>
       <c r="S32" s="4" t="inlineStr"/>
       <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="n">
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="4" t="n">
+      <c r="AB32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC32" s="7" t="inlineStr">
+      <c r="AD32" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD32" s="4" t="inlineStr"/>
-      <c r="AE32" s="4" t="inlineStr">
+      <c r="AE32" s="4" t="inlineStr"/>
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF32" s="4" t="inlineStr">
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>• Сайт mbzuai.ac.ae заблокирован Cloudflare (403) — контакты не проверены напрямую
 • По поисковой выдаче страницы mbzuai.ac.ae/about/contact: info@mbzuai.ac.ae, тел. +971 2 811 3333 (не подтверждено открытием страницы)
@@ -7139,19 +7356,19 @@
 • Узкопрофильный вуз (только ИИ), profile_type условно technical</t>
         </is>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
+      <c r="AH32" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Mohamed_bin_Zayed_University_of_Artificial_Intelligence
 • Https://library.mbzuai.ac.ae/contact-us
 • Https://www.mediaoffice.abudhabi/en/education/mbzuai-appoints-world-renowned-leading-ai/</t>
         </is>
       </c>
-      <c r="AH32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI32" s="4" t="inlineStr"/>
+      <c r="AI32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -7213,63 +7430,68 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr"/>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>info@mbru.ac.ae</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>800 6278 (800 MBRU)</t>
         </is>
       </c>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>https://www.mbru.ac.ae</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Dr. Amer Sharif</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="R33" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R33" s="4" t="inlineStr"/>
       <c r="S33" s="4" t="inlineStr"/>
       <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="n">
+      <c r="U33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="n">
+      <c r="AB33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC33" s="7" t="inlineStr">
+      <c r="AD33" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD33" s="4" t="inlineStr">
+      <c r="AE33" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE33" s="4" t="inlineStr">
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF33" s="4" t="inlineStr">
+      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>• Входит в Dubai Health (государственная академическая система здравоохранения Дубая); канцлер — шейх Ахмед бин Саид Аль Мактум
 • Есть Vice President - Partnerships: Isabel Jennings (e-mail не опубликован) — логичный адресат по партнёрствам
@@ -7277,19 +7499,19 @@
 • Медицинский профиль; nanosats.csv (UAE): записей нет</t>
         </is>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
+      <c r="AH33" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mbru.ac.ae/contact-us/
 • Https://www.mbru.ac.ae/about-mbru/our-leadership/
 • Https://www.mbru.ac.ae/about-mbru/</t>
         </is>
       </c>
-      <c r="AH33" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI33" s="4" t="inlineStr"/>
+      <c r="AI33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -7347,80 +7569,85 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>info@murdochuniversitydubai.com</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>+971 4 574 9800</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>https://www.murdochuniversitydubai.com</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Prof. Michael Gallimore</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>Dean and Academic President</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr"/>
       <c r="S34" s="4" t="inlineStr"/>
       <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="n">
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
-      <c r="AB34" s="4" t="n">
+      <c r="AB34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC34" s="7" t="inlineStr">
+      <c r="AD34" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr">
+      <c r="AE34" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF34" s="4" t="inlineStr">
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>• Кампус австралийского Murdoch University (Перт)
 • Main_fields — ориентировочно; nanosats.csv (UAE): записей нет</t>
         </is>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
+      <c r="AH34" s="4" t="inlineStr">
         <is>
           <t>• Https://www.murdochuniversitydubai.com/
 • Https://www.murdochuniversitydubai.com/explore/about/</t>
         </is>
       </c>
-      <c r="AH34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="inlineStr"/>
+      <c r="AI34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -7482,82 +7709,87 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr"/>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>info@rakmhsu.ac.ae</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>+971 7 204 3000</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>https://www.rakmhsu.ac.ae</t>
         </is>
       </c>
-      <c r="P35" s="4" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>Prof. Ismail Ibrahim Ali Matalka</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="inlineStr">
+      <c r="R35" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R35" s="4" t="inlineStr"/>
       <c r="S35" s="4" t="inlineStr"/>
       <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="n">
+      <c r="U35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="inlineStr"/>
       <c r="AA35" s="4" t="inlineStr"/>
-      <c r="AB35" s="4" t="n">
+      <c r="AB35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC35" s="7" t="inlineStr">
+      <c r="AD35" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD35" s="4" t="inlineStr">
+      <c r="AE35" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE35" s="4" t="inlineStr">
+      <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF35" s="4" t="inlineStr">
+      <c r="AG35" s="4" t="inlineStr">
         <is>
           <t>• Основан в 2006 г. под патронатом правителя Рас-эль-Хаймы шейха Сауда бин Сакра Аль-Касими; форма собственности на сайте явно не указана
 • THE2027: Reporter (без ранга)
 • Медицинский профиль — космическая тематика маловероятна; nanosats.csv (UAE): записей нет</t>
         </is>
       </c>
-      <c r="AG35" s="4" t="inlineStr">
+      <c r="AH35" s="4" t="inlineStr">
         <is>
           <t>• Https://www.rakmhsu.ac.ae/contact
 • Https://www.rakmhsu.ac.ae/university-leadership
 • Https://www.rakmhsu.ac.ae/about</t>
         </is>
       </c>
-      <c r="AH35" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI35" s="4" t="inlineStr"/>
+      <c r="AI35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -7620,67 +7852,72 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L36" s="4" t="inlineStr"/>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr">
         <is>
           <t>info@ra.ac.ae</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>+971 2 599 9111</t>
         </is>
       </c>
-      <c r="O36" s="4" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>https://www.ra.ac.ae</t>
         </is>
       </c>
-      <c r="P36" s="4" t="inlineStr">
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>James Anthony Morse</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="R36" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R36" s="4" t="inlineStr"/>
-      <c r="S36" s="4" t="inlineStr">
+      <c r="S36" s="4" t="inlineStr"/>
+      <c r="T36" s="4" t="inlineStr">
         <is>
           <t>THE2027: Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T36" s="4" t="inlineStr"/>
-      <c r="U36" s="4" t="n">
+      <c r="U36" s="4" t="inlineStr"/>
+      <c r="V36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="4" t="inlineStr"/>
       <c r="W36" s="4" t="inlineStr"/>
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="inlineStr"/>
       <c r="AA36" s="4" t="inlineStr"/>
-      <c r="AB36" s="4" t="n">
+      <c r="AB36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC36" s="7" t="inlineStr">
+      <c r="AD36" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD36" s="4" t="inlineStr">
+      <c r="AE36" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE36" s="4" t="inlineStr">
+      <c r="AF36" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF36" s="4" t="inlineStr">
+      <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>• Академия безопасности, обороны и кризисного управления; учреждена Законом № 7 от 2013 г. (шейх Халифа бин Заед) — тип собственности «эмират Абу-Даби» — проверить
 • Учёная степень/титул президента на странице не указаны — обращение без «Prof./Dr.»
@@ -7689,7 +7926,7 @@
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
         </is>
       </c>
-      <c r="AG36" s="4" t="inlineStr">
+      <c r="AH36" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ra.ac.ae/en/about-rabdan/leadership-team
 • Https://www.ra.ac.ae/en/contact-us
@@ -7697,12 +7934,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI36" s="4" t="inlineStr"/>
+      <c r="AI36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -7760,82 +7997,87 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>dubai@rit.edu</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>+971 4 371 2000</t>
         </is>
       </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>https://www.rit.edu/dubai/</t>
-        </is>
-      </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
+          <t>https://www.rit.edu/dubai</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
           <t>Dr. Yousef Al-Assaf</t>
         </is>
       </c>
-      <c r="Q37" s="4" t="inlineStr">
+      <c r="R37" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr"/>
       <c r="S37" s="4" t="inlineStr"/>
       <c r="T37" s="4" t="inlineStr"/>
-      <c r="U37" s="4" t="n">
+      <c r="U37" s="4" t="inlineStr"/>
+      <c r="V37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="inlineStr"/>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="inlineStr"/>
       <c r="AA37" s="4" t="inlineStr"/>
-      <c r="AB37" s="4" t="n">
+      <c r="AB37" s="4" t="inlineStr"/>
+      <c r="AC37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC37" s="7" t="inlineStr">
+      <c r="AD37" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD37" s="4" t="inlineStr">
+      <c r="AE37" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE37" s="4" t="inlineStr">
+      <c r="AF37" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF37" s="4" t="inlineStr">
+      <c r="AG37" s="4" t="inlineStr">
         <is>
           <t>• Глобальный кампус RIT (Рочестер, США), отчитывается перед RIT NY; совет директоров включает представителей Dubai Silicon Oasis Authority
 • Сведения о спутниках RIT Dubai не найдены; nanosats.csv (UAE): записей нет
 • Арабское официальное название на сайте не найдено</t>
         </is>
       </c>
-      <c r="AG37" s="4" t="inlineStr">
+      <c r="AH37" s="4" t="inlineStr">
         <is>
           <t>• Https://www.rit.edu/dubai/
 • Https://www.rit.edu/dubai/about-rit
 • Https://www.rit.edu/dubai/board-directors</t>
         </is>
       </c>
-      <c r="AH37" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI37" s="4" t="inlineStr"/>
+      <c r="AI37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -7888,59 +8130,64 @@
       </c>
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M38" s="4" t="inlineStr"/>
-      <c r="N38" s="4" t="inlineStr">
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>+971 2 656 9330</t>
         </is>
       </c>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>https://www.sorbonne.ae</t>
         </is>
       </c>
-      <c r="P38" s="4" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>Prof. Nathalie Martial-Braz</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="inlineStr">
+      <c r="R38" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr"/>
-      <c r="S38" s="4" t="inlineStr">
+      <c r="S38" s="4" t="inlineStr"/>
+      <c r="T38" s="4" t="inlineStr">
         <is>
           <t>THE2027: Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="n">
+      <c r="U38" s="4" t="inlineStr"/>
+      <c r="V38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="4" t="inlineStr"/>
       <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="inlineStr"/>
       <c r="AA38" s="4" t="inlineStr"/>
-      <c r="AB38" s="4" t="n">
+      <c r="AB38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC38" s="7" t="inlineStr">
+      <c r="AD38" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD38" s="4" t="inlineStr"/>
-      <c r="AE38" s="4" t="inlineStr">
+      <c r="AE38" s="4" t="inlineStr"/>
+      <c r="AF38" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF38" s="4" t="inlineStr">
+      <c r="AG38" s="4" t="inlineStr">
         <is>
           <t>• Кампус французских университетов (Sorbonne Université, Université Paris Cité и др.), финансируется правительством Абу-Даби — тип «кампус иностранного вуза» условен
 • E-mail на сайте не опубликован (только формы); второй телефон +971 2 656 9555
@@ -7949,7 +8196,7 @@
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
         </is>
       </c>
-      <c r="AG38" s="4" t="inlineStr">
+      <c r="AH38" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sorbonne.ae/about-us/governance/university-leadership
 • Https://www.sorbonne.ae/contact-us
@@ -7957,12 +8204,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI38" s="4" t="inlineStr"/>
+      <c r="AI38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -8022,81 +8269,86 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L39" s="4" t="inlineStr"/>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr">
         <is>
           <t>info@buid.ac.ae</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>+971 4 279 1400</t>
         </is>
       </c>
-      <c r="O39" s="4" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>https://www.buid.ac.ae</t>
         </is>
       </c>
-      <c r="P39" s="4" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>Prof. Abdullah M. Alshamsi</t>
         </is>
       </c>
-      <c r="Q39" s="4" t="inlineStr">
+      <c r="R39" s="4" t="inlineStr">
         <is>
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R39" s="4" t="inlineStr"/>
       <c r="S39" s="4" t="inlineStr"/>
       <c r="T39" s="4" t="inlineStr"/>
-      <c r="U39" s="4" t="n">
+      <c r="U39" s="4" t="inlineStr"/>
+      <c r="V39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="inlineStr"/>
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="inlineStr"/>
       <c r="AA39" s="4" t="inlineStr"/>
-      <c r="AB39" s="4" t="n">
+      <c r="AB39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC39" s="7" t="inlineStr">
+      <c r="AD39" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD39" s="4" t="inlineStr">
+      <c r="AE39" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE39" s="4" t="inlineStr">
+      <c r="AF39" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF39" s="4" t="inlineStr">
+      <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>• Сайт buid.ac.ae блокирует автоматический доступ (403); контакты взяты из Undergraduate Student Handbook (сент. 2026)
 • Канцлер — шейх Ахмед бин Саид Аль Мактум
 • THE2027: Reporter (без ранга); nanosats.csv (UAE): записей нет</t>
         </is>
       </c>
-      <c r="AG39" s="4" t="inlineStr">
+      <c r="AH39" s="4" t="inlineStr">
         <is>
           <t>• Https://www.buid.ac.ae/wp-content/uploads/Handbooks/UG-Handbook.pdf
 • Https://mediaoffice.ae/en/news/2026/april/30-04/the-community-development-authority-in-dubai-and-the-british-university-in-dubai-sign</t>
         </is>
       </c>
-      <c r="AH39" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI39" s="4" t="inlineStr"/>
+      <c r="AI39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8148,51 +8400,56 @@
       </c>
       <c r="J40" s="4" t="inlineStr"/>
       <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M40" s="4" t="inlineStr"/>
       <c r="N40" s="4" t="inlineStr"/>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>https://www.uowdubai.ac.ae</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohamed-Vall M. Salem Zein</t>
         </is>
       </c>
-      <c r="Q40" s="4" t="inlineStr">
+      <c r="R40" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R40" s="4" t="inlineStr"/>
       <c r="S40" s="4" t="inlineStr"/>
       <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="n">
+      <c r="U40" s="4" t="inlineStr"/>
+      <c r="V40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="4" t="inlineStr"/>
       <c r="W40" s="4" t="inlineStr"/>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="inlineStr"/>
       <c r="AA40" s="4" t="inlineStr"/>
-      <c r="AB40" s="4" t="n">
+      <c r="AB40" s="4" t="inlineStr"/>
+      <c r="AC40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC40" s="7" t="inlineStr">
+      <c r="AD40" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD40" s="4" t="inlineStr"/>
-      <c r="AE40" s="4" t="inlineStr">
+      <c r="AE40" s="4" t="inlineStr"/>
+      <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF40" s="4" t="inlineStr">
+      <c r="AG40" s="4" t="inlineStr">
         <is>
           <t>• Сайт uowdubai.ac.ae блокирует автоматический доступ (403) — e-mail, телефон и P.O. Box не проверены
 • Автономный кампус University of Wollongong (Австралия), президент с 2015 г
@@ -8200,21 +8457,21 @@
 • Перепроверка: uowdubai.ac.ae (главная, /contact-us, sitemap) и WebFetch возвращают 403 — данные не изменены (04.10.2026)</t>
         </is>
       </c>
-      <c r="AG40" s="4" t="inlineStr">
+      <c r="AH40" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uow.edu.au/the-stand/2025/branching-out-growing-uows-global-reach-in-dubai.php
 • Https://en.wikipedia.org/wiki/University_of_Wollongong_in_Dubai</t>
         </is>
       </c>
-      <c r="AH40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI40" s="4" t="inlineStr"/>
+      <c r="AI40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ40" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI40"/>
+  <autoFilter ref="A1:AJ40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/research/brics_universities/output/BRICS_universities_uae.xlsx
+++ b/research/brics_universities/output/BRICS_universities_uae.xlsx
@@ -12,8 +12,8 @@
     <sheet name="ОАЭ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AJ$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ОАЭ'!$A$1:$AJ$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AK$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ОАЭ'!$A$1:$AK$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ11"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -676,21 +676,22 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="55" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,75 +802,80 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Рейтинг Webometrics (мир)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -977,11 +983,20 @@
           <t>THE2027: =235</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• MYSAT-1 (2018)
 • MeznSat (2020)
@@ -989,17 +1004,17 @@
 • Light-1 (2021)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>6U CubeSat с собственной экологичной HTP-двигательной установкой (совместно с UAE Space Agency, запуск ожидался к концу 2026)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Наземная станция KU Space Technology and Innovation Lab (указана на странице facilities; параметры не раскрыты)</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>• Khalifa University Space Technology and Innovation Center (KUSTIC)
 • Khalifa University Space Technology and Innovation Lab (KUSTIL)
@@ -1007,7 +1022,7 @@
 • Thermal vacuum chamber &amp; cleanroom</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency
 • Yahsat (Al Yah Satellite Communications)
@@ -1017,35 +1032,36 @@
 • American University of Ras Al Khaimah (MeznSat)</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Председатель Попечительского совета — Шейх Хамед бин Заед Аль Нахайян (H.H. Sheikh Hamed bin Zayed Al Nahyan); исполнительный глава — президент Prof. Ebrahim Al Hajri
 • Отдельный e-mail международного офиса не опубликован; isso@ku.ac.ae и studyabroad@ku.ac.ae — студенческие службы. Для партнёрства — info@ku.ac.ae; профильный руководитель — Dr. Ashraf Al Najdawi, Vice President, External Relations
 • MeznSat формально Masdar Institute (ныне в составе KU) + AURAK; Light-1 — совместно с NYUAD и NSSA (Бахрейн)
 • Наиболее сильный космический профиль среди вузов ОАЭ — приоритетный партнёр для CubeSat-группировки
-• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
-        </is>
-      </c>
-      <c r="AH2" s="4" t="inlineStr">
+• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)
+• Рейтинги: QS: в таблице как «Khalifa University»; THE: в таблице как «Khalifa University»; Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ku.ac.ae/university-leadership
 • Https://www.ku.ac.ae/contact-us
@@ -1053,15 +1069,19 @@
 • Https://www.ku.ac.ae/research-centers/khalifa-university-space-technology-and-innovation-group/facilities
 • Https://www.ku.ac.ae/kustil/news
 • Https://satelliteprome.com/news/uae-entities-partner-to-establish-khalifa-university-space-technology-and-innovation-centre/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1140,13 +1160,30 @@
           <t>Director General</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• DubaiSat-1 (2009)
 • DubaiSat-2 (2013)
@@ -1162,19 +1199,19 @@
 • HCT-SAT 2 (2025)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>• PHI-2…PHI-5 (12U, Payload Hosting Initiative, with NanoAvionics)
 • Emirates Airlock for NASA Lunar Gateway
 • Rashid rover programme</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>MBRSC ground station (Al Khawaneej, Dubai) — offers ground station services</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Satellite Development Programme
 • UAE Astronaut Programme
@@ -1182,7 +1219,7 @@
 • Payload Hosting Initiative (PHI)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>• UNOOSA (PHI, 'Access to Space for All')
 • NASA (astronaut training, Lunar Gateway Emirates Airlock)
@@ -1192,45 +1229,47 @@
 • Satrec Initiative (DubaiSat, Etihad-SAT)</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Не университет, а государственное космическое агентство эмирата Дубай (включено намеренно); председатель — H.E. Hamad Obaid Al Mansoori
 • E-mail на официальном сайте не опубликован; сторонние источники (Bayut и др.) указывают info@mbrsc.ae — не проверено на официальной странице
 • Программа PHI (UNOOSA) — готовый механизм размещения полезных нагрузок партнёров на 12U-платформе; уже принимала нагрузки Бахрейна и Непала — естественная точка входа для сотрудничества
-• Etihad-SAT: на сайте MBRSC указан запуск в марте 2025; HCT-SAT 2 и PHI-Demo — по nanosats.csv; Hope Probe — марсианский орбитальный аппарат (не CubeSat)</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
+• Etihad-SAT: на сайте MBRSC указан запуск в марте 2025; HCT-SAT 2 и PHI-Demo — по nanosats.csv; Hope Probe — марсианский орбитальный аппарат (не CubeSat)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mbrsc.ae/contact-us/
 • Https://www.mbrsc.ae/about/
 • Https://www.mbrsc.ae/satellites/
 • Https://www.mbrsc.ae/missions-and-projects/
 • Https://www.mbrsc.ae/lunar-gateway/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1334,66 +1373,76 @@
           <t>THE2027: =235</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>• ALainSat-1 (2025)
 • LEONAV-1 (2026)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>813 Satellite (Arab Satellite 813, EO, Arab cooperation project)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>NSSTC Ground Segment at UAEU (Al Ain): S/X-band dish antennas + UHF antenna</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>National Space Science and Technology Center (NSSTC)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (NSSTC co-founder)
 • Telecommunications and Digital Government Regulatory Authority (ICT Fund, NSSTC co-founder)
 • IEEE GRSS (AlAinSat-1 payloads)</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Канцлер (Chancellor) — H.E. Zaki Anwar Nusseibeh; исполнительный руководитель — вице-канцлер Prof. Ahmed Ali Alraeesi
 • Отдельный e-mail международного офиса на сайте не найден; servicedesk@uaeu.ac.ae — общий сервис-деск. Для космической тематики лучше параллельно писать в NSSTC: nsstc@uaeu.ac.ae
 • NSSTC — ключевой контакт: ALainSat-1 (запуск 14.01.2025, Transporter-12, совместно с IEEE GRSS), LEONAV-1 (07.07.2026, Transporter-17, навигационный демонстратор); GNSSaS A/B отменены
-• MeznSat (2020) построен Khalifa University и AURAK, не UAEU</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
+• MeznSat (2020) построен Khalifa University и AURAK, не UAEU
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uaeu.ac.ae/en/contact/index.shtml
 • Https://www.uaeu.ac.ae/en/vc/index.shtml
@@ -1402,15 +1451,19 @@
 • Https://nsstc.uaeu.ac.ae/en/ground-segment.shtml
 • Https://nsstc.uaeu.ac.ae/en/alainsat-1.shtml
 • Https://nsstc.uaeu.ac.ae/en/about/index.shtml
-• Https://www.emirates247.com/uae/uaeu-announces-successful-launch-of-leonav-1-satellite/3485</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr">
+• Https://www.emirates247.com/uae/uaeu-announces-successful-launch-of-leonav-1-satellite/3485
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1511,7 +1564,7 @@
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 283</t>
+          <t>QS2027: =283</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
@@ -1519,28 +1572,37 @@
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>• Sharjah-Sat-1 (2023)
 • Sharjah-Sat-2 (2026)</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>4.5 m S-band ground station (SAASST) для серии Sharjah-Sat</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Sharjah Academy for Astronomy, Space Sciences and Technology (SAASST)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>• Innovative Solutions in Space (ISISpace, Нидерланды) — Sharjah-Sat-2
 • Sharjah Municipality
@@ -1549,35 +1611,36 @@
 • SpaceX (запуски)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AD5" s="5" t="inlineStr">
+      <c r="AE5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Президент (учредитель) университета — Шейх д-р Султан бин Мухаммад аль-Касими, правитель Шарджи; исполнительный глава — канцлер Prof. Esameldin Agamy
 • Тип собственности указан как «эмират Шарджа» (вне стандартного списка) — университет учреждён правителем Шарджи
 • Телефон Office of International Relations: +971 6 505 0529. Действующий директор OIR на сайте не указан (в каталоге 2023–2024 — Dr. Tarek Merabtene, не подтверждено на 2025–2026)
 • Sharjah-Sat-2 запущен 30.03.2026 (Falcon 9, Transporter-16)
-• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sharjah.ac.ae/en/Discover-UoS/Senior-Administration
 • Https://www.sharjah.ac.ae/en/Discover-UoS/Contact-Us
@@ -1585,15 +1648,19 @@
 • Https://www.sharjah.ac.ae/News/SAASST-Establishes-S-Band-Ground-Station-for
 • Https://spacetech-gulf.com/2026/04/sharjahsat-2-successfully-launched-strengthening-uaes-earth-observation-capabilities/
 • Https://www.thenationalnews.com/news/uae/2025/12/20/sharjah-mini-satellite-primed-to-boost-disaster-response-begins-final-tests-for-2026-launch/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1686,75 +1753,96 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: =608</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>MeznSat (2020)</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>AURAK space lab ground station (used for MeznSat)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>AURAK Space Lab (School of Engineering)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (MeznSat sponsor/supervisor)
 • Khalifa University (MeznSat partner)</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AD6" s="5" t="inlineStr">
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE6" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• THE2027: Reporter (без ранга); в QS2027 топ-500 отсутствует
 • MeznSat (3U, 28.09.2020, Союз/Плесецк) построен 16 студентами AURAK (руководитель Dr. Abdul-Halim Jallad) совместно с Khalifa University под эгидой UAE Space Agency; в nanosats.csv записан на Masdar Institute
 • Международный офис не идентифицирован (OIAER/OISE — расшифровка не подтверждена); прямой e-mail президента: bassam.alameddine@aurak.ac.ae
-• Сайт защищён капчей — данные получены через WebFetch</t>
-        </is>
-      </c>
-      <c r="AH6" s="4" t="inlineStr">
+• Сайт защищён капчей — данные получены через WebFetch
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI6" s="4" t="inlineStr">
         <is>
           <t>• Https://aurak.ac.ae/contact
 • Https://aurak.ac.ae/about/leadership/leadership-team
 • Https://aurak.ac.ae/en/aurak-news-sept-28-2020
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1849,7 +1937,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 258</t>
+          <t>QS2027: =258</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -1857,70 +1945,84 @@
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>Nayif-1 (2017)</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>AUS ground station (UHF, used to operate Nayif-1)</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t>Mohammed Bin Rashid Space Centre (MBRSC) — Nayif-1 partner and MoU</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Основатель и президент университета — Его Высочество шейх д-р Султан бин Мухаммед Аль-Касими, правитель Шарджи; исполнительный руководитель — канцлер Dr. Tod A. Laursen
 • Nayif-1 (2017) — первый наноспутник ОАЭ, построен студентами AUS совместно с MBRSC и ISIS; наземная станция на кампусе AUS
 • Общий e-mail не опубликован (только формат name@aus.edu); канцелярия канцлера: Chief of Staff Dr. Daniel Lincoln, dlincoln@aus.edu
-• Ixo@aus.edu — International Exchange Office (студенческие обмены); руководитель офиса на сайте не указан (указаны Advisor Grace Morales, Coordinator Lillie De Guzman)</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
+• Ixo@aus.edu — International Exchange Office (студенческие обмены); руководитель офиса на сайте не указан (указаны Advisor Grace Morales, Coordinator Lillie De Guzman)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aus.edu/contact-us
 • Https://www.aus.edu/leadership-cabinet/tod-a-laursen
 • Https://www.aus.edu/about/leadership/office-of-the-chancellor/chancellors-staff
 • Https://www.aus.edu/academics/international-study-and-exchange/contact-department-of-international-studies
 • Https://www.aus.edu/the-road-to-launching-nayif-1-the-uaes-first-nanosatellite
-• Https://www.mbrsc.ae/satellites/</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr">
+• Https://www.mbrsc.ae/satellites/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -2011,75 +2113,95 @@
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>Light-1 (2021) — полезная нагрузка RAAD (совместно с Khalifa University)</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr"/>
       <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• Center for Astrophysics and Space Science (CASS)
 • PhD program in Astrophysics and Space Systems (с 2025)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (соглашение 2026 по данным Emirates Mars Mission)
 • Khalifa University
 • National Space Science Agency of Bahrain (Light-1)</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
+      <c r="AE8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Кампус Нью-Йоркского университета (США); NYUAD не ранжируется QS/THE отдельно (рейтинг у NYU в целом)
 • Prof. Fabio Piano — Vice Chancellor с 06.08.2026 (ранее провост 2010–2020)
 • Light-1: NYUAD разработал научную нагрузку RAAD, платформу собирал Khalifa University — спутник засчитан как совместный
 • Отдельный e-mail международного/партнёрского офиса не найден; использован e-mail офиса вице-канцлера. По поиску: общий nyuad@nyu.edu и тел. +971 2 628 4000 (на открытых страницах не подтверждено)
-• Американское юрлицо материнского вуза — возможны ограничения экспортного контроля США при космическом сотрудничестве</t>
-        </is>
-      </c>
-      <c r="AH8" s="4" t="inlineStr">
+• Американское юрлицо материнского вуза — возможны ограничения экспортного контроля США при космическом сотрудничестве
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>• Https://nyuad.nyu.edu/en/about/leadership-and-people/office-of-the-vice-chancellor.html
 • Https://nyuad.nyu.edu/en/research/facilities-and-support/participate-in-research-studies/contacts-and-locations.html
 • Https://nyuad.nyu.edu/en/news/latest-news/science-and-technology/2026/june/nyuad-and-uae-space-agency-cooperation-mars-mission.html
 • Https://nyuad.nyu.edu/en/news/latest-news/science-and-technology/2022/february/cubesat-launch-iss.html
-• Https://www.ku.ac.ae/kustil/news</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr">
+• Https://www.ku.ac.ae/kustil/news
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -2174,70 +2296,90 @@
           <t>President &amp; CEO</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="n">
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr">
         <is>
           <t>• HCT-SAT 1 (2025)
 • HCT-SAT 2 (2025)</t>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
       <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
         <is>
           <t>Mohammed Bin Rashid Space Centre (MBRSC)</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AD9" s="5" t="inlineStr">
+      <c r="AE9" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Канцлер — H.E. Dr. Ahmad Belhoul Al Falasi (министр спорта ОАЭ); исполнительный глава — President &amp; CEO Dr. Faisal Alayyan
 • HCT-SAT 1/2 — 1U CubeSat, построены студентами HCT совместно с MBRSC (MBRSC — сборка, испытания, запуск и связь). HCT-SAT 1 (Transporter-12, 14.01.2025) — по nanosats.csv сигнала нет; HCT-SAT 2 — 28.11.2025, работает
 • Сеть колледжей с кампусами в нескольких эмиратах; на сайте указан только P.O. Box 25026 без эмирата; город (Абу-Даби, центральный офис) — проверить
 • Международного офиса/e-mail не найдено; партнёрства ведёт Partnerships Management Department; использован общий communication@hct.ac.ae
-• Телефон — бесплатная линия ОАЭ 800 663428 (из-за рубежа может не работать)</t>
-        </is>
-      </c>
-      <c r="AH9" s="4" t="inlineStr">
+• Телефон — бесплатная линия ОАЭ 800 663428 (из-за рубежа может не работать)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
         <is>
           <t>• Https://hct.ac.ae/en/about-hct/president-ceos-message/
 • Https://hct.ac.ae/en/about-hct/hct-leadership/
 • Https://hct.ac.ae/en/contact-us/
 • Https://db.satnogs.org/satellite/98470/
 • Https://www.khaleejtimes.com/space/uae-made-mbz-sat-to-blast-off-in-january-2025-from-california
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr">
+• Nanosats.csv
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -2330,68 +2472,87 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
+      <c r="X10" s="4" t="inlineStr"/>
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>MAHASAT — студенческая программа пикоспутников (2023: испытания 5 пикоспутников на дроне-«носителе», не орбитальные)</t>
         </is>
       </c>
-      <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="AA10" s="4" t="inlineStr">
         <is>
           <t>• Centre for Satellite Communications
 • MAHASAT student pico-satellite programme (рук. Mylswamy Annadurai, экс-директор URSC ISRO)</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr"/>
       <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="n">
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AD10" s="6" t="inlineStr">
+      <c r="AE10" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Кампус индийского BITS Pilani; name_native дан на английском (официальное наименование), арабского официального названия не найдено
 • Директор Prof. Souri Banerjee (назначен в 2024 г., сменил Prof. Srinivasan Madapusi, ныне Pro VC Amity Dubai) — подтверждено Википедией и пресс-релизами, на сайте кампуса имя не найдено
 • E-mail международного офиса не найден; использован e-mail офиса регистратора. Доп. тел. +971 4 275 3711
 • Есть интерес к малым спутникам (MAHASAT, связь с экс-руководством ISRO) — перспективный кандидат при наличии индийских связей
-• Поисковая квота исчерпана — орбитальные запуски MAHASAT после 2023 г. не проверены (в nanosats.csv отсутствуют)</t>
-        </is>
-      </c>
-      <c r="AH10" s="4" t="inlineStr">
+• Поисковая квота исчерпана — орбитальные запуски MAHASAT после 2023 г. не проверены (в nanosats.csv отсутствуют)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI10" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bits-pilani.ac.in/dubai/
 • Https://en.wikipedia.org/wiki/Birla_Institute_of_Technology_and_Science,_Pilani_%E2%80%93_Dubai_Campus
 • Https://gulfnews.com/uae/education/bits-pilani-dubai-campus-appoints-new-director-1.81511128
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2467,64 +2628,83 @@
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="n">
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>Abu Dhabi Quantum Optical Ground Station (ADQOGS) — optical/quantum free-space communications</t>
         </is>
       </c>
-      <c r="Z11" s="4" t="inlineStr">
+      <c r="AA11" s="4" t="inlineStr">
         <is>
           <t>Propulsion and Space Research Center (Chief Researcher Dr. Elias Tsoutsanis)</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="inlineStr"/>
       <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AD11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AD11" s="6" t="inlineStr">
+      <c r="AE11" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Не университет — исследовательский центр при ATRC (Advanced Technology Research Council) Абу-Даби, включён намеренно
 • E-mail и телефон на сайте не опубликованы (только веб-форма)
-• Космос: собственных спутников нет; в 2026 г. испытан первый в ОАЭ гибридный суборбитальный ракетный двигатель/ракета; оптическая квантовая наземная станция ADQOGS — потенциальный интерес для связи с CubeSat</t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr">
+• Космос: собственных спутников нет; в 2026 г. испытан первый в ОАЭ гибридный суборбитальный ракетный двигатель/ракета; оптическая квантовая наземная станция ADQOGS — потенциальный интерес для связи с CubeSat
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tii.ae/contact-us
 • Https://www.tii.ae/about-us
 • Https://www.tii.ae/insights/abu-dhabi-test-launches-first-fully-uae-built-hybrid-rocket-milestone-space-ambitions
-• Https://www.mediaoffice.abudhabi/en/technology/technology-innovation-institute-launches-abu-dhabi-quantum-optical-ground-station/</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr">
+• Https://www.mediaoffice.abudhabi/en/technology/technology-innovation-institute-launches-abu-dhabi-quantum-optical-ground-station/
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ11"/>
+  <autoFilter ref="A1:AK11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2535,7 +2715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AK40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2559,21 +2739,22 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="55" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2684,75 +2865,80 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Рейтинг Webometrics (мир)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -2860,11 +3046,20 @@
           <t>THE2027: =235</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• MYSAT-1 (2018)
 • MeznSat (2020)
@@ -2872,17 +3067,17 @@
 • Light-1 (2021)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>6U CubeSat с собственной экологичной HTP-двигательной установкой (совместно с UAE Space Agency, запуск ожидался к концу 2026)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Наземная станция KU Space Technology and Innovation Lab (указана на странице facilities; параметры не раскрыты)</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>• Khalifa University Space Technology and Innovation Center (KUSTIC)
 • Khalifa University Space Technology and Innovation Lab (KUSTIL)
@@ -2890,7 +3085,7 @@
 • Thermal vacuum chamber &amp; cleanroom</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency
 • Yahsat (Al Yah Satellite Communications)
@@ -2900,35 +3095,36 @@
 • American University of Ras Al Khaimah (MeznSat)</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Председатель Попечительского совета — Шейх Хамед бин Заед Аль Нахайян (H.H. Sheikh Hamed bin Zayed Al Nahyan); исполнительный глава — президент Prof. Ebrahim Al Hajri
 • Отдельный e-mail международного офиса не опубликован; isso@ku.ac.ae и studyabroad@ku.ac.ae — студенческие службы. Для партнёрства — info@ku.ac.ae; профильный руководитель — Dr. Ashraf Al Najdawi, Vice President, External Relations
 • MeznSat формально Masdar Institute (ныне в составе KU) + AURAK; Light-1 — совместно с NYUAD и NSSA (Бахрейн)
 • Наиболее сильный космический профиль среди вузов ОАЭ — приоритетный партнёр для CubeSat-группировки
-• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
-        </is>
-      </c>
-      <c r="AH2" s="4" t="inlineStr">
+• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)
+• Рейтинги: QS: в таблице как «Khalifa University»; THE: в таблице как «Khalifa University»; Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ku.ac.ae/university-leadership
 • Https://www.ku.ac.ae/contact-us
@@ -2936,15 +3132,19 @@
 • Https://www.ku.ac.ae/research-centers/khalifa-university-space-technology-and-innovation-group/facilities
 • Https://www.ku.ac.ae/kustil/news
 • Https://satelliteprome.com/news/uae-entities-partner-to-establish-khalifa-university-space-technology-and-innovation-centre/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -3023,13 +3223,30 @@
           <t>Director General</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• DubaiSat-1 (2009)
 • DubaiSat-2 (2013)
@@ -3045,19 +3262,19 @@
 • HCT-SAT 2 (2025)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>• PHI-2…PHI-5 (12U, Payload Hosting Initiative, with NanoAvionics)
 • Emirates Airlock for NASA Lunar Gateway
 • Rashid rover programme</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>MBRSC ground station (Al Khawaneej, Dubai) — offers ground station services</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Satellite Development Programme
 • UAE Astronaut Programme
@@ -3065,7 +3282,7 @@
 • Payload Hosting Initiative (PHI)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>• UNOOSA (PHI, 'Access to Space for All')
 • NASA (astronaut training, Lunar Gateway Emirates Airlock)
@@ -3075,45 +3292,47 @@
 • Satrec Initiative (DubaiSat, Etihad-SAT)</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Не университет, а государственное космическое агентство эмирата Дубай (включено намеренно); председатель — H.E. Hamad Obaid Al Mansoori
 • E-mail на официальном сайте не опубликован; сторонние источники (Bayut и др.) указывают info@mbrsc.ae — не проверено на официальной странице
 • Программа PHI (UNOOSA) — готовый механизм размещения полезных нагрузок партнёров на 12U-платформе; уже принимала нагрузки Бахрейна и Непала — естественная точка входа для сотрудничества
-• Etihad-SAT: на сайте MBRSC указан запуск в марте 2025; HCT-SAT 2 и PHI-Demo — по nanosats.csv; Hope Probe — марсианский орбитальный аппарат (не CubeSat)</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
+• Etihad-SAT: на сайте MBRSC указан запуск в марте 2025; HCT-SAT 2 и PHI-Demo — по nanosats.csv; Hope Probe — марсианский орбитальный аппарат (не CubeSat)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mbrsc.ae/contact-us/
 • Https://www.mbrsc.ae/about/
 • Https://www.mbrsc.ae/satellites/
 • Https://www.mbrsc.ae/missions-and-projects/
 • Https://www.mbrsc.ae/lunar-gateway/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -3217,66 +3436,76 @@
           <t>THE2027: =235</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>• ALainSat-1 (2025)
 • LEONAV-1 (2026)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>813 Satellite (Arab Satellite 813, EO, Arab cooperation project)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>NSSTC Ground Segment at UAEU (Al Ain): S/X-band dish antennas + UHF antenna</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>National Space Science and Technology Center (NSSTC)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (NSSTC co-founder)
 • Telecommunications and Digital Government Regulatory Authority (ICT Fund, NSSTC co-founder)
 • IEEE GRSS (AlAinSat-1 payloads)</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="AD4" s="5" t="inlineStr">
+      <c r="AE4" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Канцлер (Chancellor) — H.E. Zaki Anwar Nusseibeh; исполнительный руководитель — вице-канцлер Prof. Ahmed Ali Alraeesi
 • Отдельный e-mail международного офиса на сайте не найден; servicedesk@uaeu.ac.ae — общий сервис-деск. Для космической тематики лучше параллельно писать в NSSTC: nsstc@uaeu.ac.ae
 • NSSTC — ключевой контакт: ALainSat-1 (запуск 14.01.2025, Transporter-12, совместно с IEEE GRSS), LEONAV-1 (07.07.2026, Transporter-17, навигационный демонстратор); GNSSaS A/B отменены
-• MeznSat (2020) построен Khalifa University и AURAK, не UAEU</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
+• MeznSat (2020) построен Khalifa University и AURAK, не UAEU
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uaeu.ac.ae/en/contact/index.shtml
 • Https://www.uaeu.ac.ae/en/vc/index.shtml
@@ -3285,15 +3514,19 @@
 • Https://nsstc.uaeu.ac.ae/en/ground-segment.shtml
 • Https://nsstc.uaeu.ac.ae/en/alainsat-1.shtml
 • Https://nsstc.uaeu.ac.ae/en/about/index.shtml
-• Https://www.emirates247.com/uae/uaeu-announces-successful-launch-of-leonav-1-satellite/3485</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr">
+• Https://www.emirates247.com/uae/uaeu-announces-successful-launch-of-leonav-1-satellite/3485
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3394,7 +3627,7 @@
       </c>
       <c r="S5" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 283</t>
+          <t>QS2027: =283</t>
         </is>
       </c>
       <c r="T5" s="4" t="inlineStr">
@@ -3402,28 +3635,37 @@
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>• Sharjah-Sat-1 (2023)
 • Sharjah-Sat-2 (2026)</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr"/>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr"/>
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>4.5 m S-band ground station (SAASST) для серии Sharjah-Sat</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>Sharjah Academy for Astronomy, Space Sciences and Technology (SAASST)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>• Innovative Solutions in Space (ISISpace, Нидерланды) — Sharjah-Sat-2
 • Sharjah Municipality
@@ -3432,35 +3674,36 @@
 • SpaceX (запуски)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="AD5" s="5" t="inlineStr">
+      <c r="AE5" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Президент (учредитель) университета — Шейх д-р Султан бин Мухаммад аль-Касими, правитель Шарджи; исполнительный глава — канцлер Prof. Esameldin Agamy
 • Тип собственности указан как «эмират Шарджа» (вне стандартного списка) — университет учреждён правителем Шарджи
 • Телефон Office of International Relations: +971 6 505 0529. Действующий директор OIR на сайте не указан (в каталоге 2023–2024 — Dr. Tarek Merabtene, не подтверждено на 2025–2026)
 • Sharjah-Sat-2 запущен 30.03.2026 (Falcon 9, Transporter-16)
-• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sharjah.ac.ae/en/Discover-UoS/Senior-Administration
 • Https://www.sharjah.ac.ae/en/Discover-UoS/Contact-Us
@@ -3468,15 +3711,19 @@
 • Https://www.sharjah.ac.ae/News/SAASST-Establishes-S-Band-Ground-Station-for
 • Https://spacetech-gulf.com/2026/04/sharjahsat-2-successfully-launched-strengthening-uaes-earth-observation-capabilities/
 • Https://www.thenationalnews.com/news/uae/2025/12/20/sharjah-mini-satellite-primed-to-boost-disaster-response-begins-final-tests-for-2026-launch/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3569,75 +3816,96 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: =608</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>MeznSat (2020)</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>AURAK space lab ground station (used for MeznSat)</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>AURAK Space Lab (School of Engineering)</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (MeznSat sponsor/supervisor)
 • Khalifa University (MeznSat partner)</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AD6" s="5" t="inlineStr">
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="AE6" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• THE2027: Reporter (без ранга); в QS2027 топ-500 отсутствует
 • MeznSat (3U, 28.09.2020, Союз/Плесецк) построен 16 студентами AURAK (руководитель Dr. Abdul-Halim Jallad) совместно с Khalifa University под эгидой UAE Space Agency; в nanosats.csv записан на Masdar Institute
 • Международный офис не идентифицирован (OIAER/OISE — расшифровка не подтверждена); прямой e-mail президента: bassam.alameddine@aurak.ac.ae
-• Сайт защищён капчей — данные получены через WebFetch</t>
-        </is>
-      </c>
-      <c r="AH6" s="4" t="inlineStr">
+• Сайт защищён капчей — данные получены через WebFetch
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI6" s="4" t="inlineStr">
         <is>
           <t>• Https://aurak.ac.ae/contact
 • Https://aurak.ac.ae/about/leadership/leadership-team
 • Https://aurak.ac.ae/en/aurak-news-sept-28-2020
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3732,7 +4000,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 258</t>
+          <t>QS2027: =258</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -3740,70 +4008,84 @@
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>Nayif-1 (2017)</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>AUS ground station (UHF, used to operate Nayif-1)</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr"/>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t>Mohammed Bin Rashid Space Centre (MBRSC) — Nayif-1 partner and MoU</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Основатель и президент университета — Его Высочество шейх д-р Султан бин Мухаммед Аль-Касими, правитель Шарджи; исполнительный руководитель — канцлер Dr. Tod A. Laursen
 • Nayif-1 (2017) — первый наноспутник ОАЭ, построен студентами AUS совместно с MBRSC и ISIS; наземная станция на кампусе AUS
 • Общий e-mail не опубликован (только формат name@aus.edu); канцелярия канцлера: Chief of Staff Dr. Daniel Lincoln, dlincoln@aus.edu
-• Ixo@aus.edu — International Exchange Office (студенческие обмены); руководитель офиса на сайте не указан (указаны Advisor Grace Morales, Coordinator Lillie De Guzman)</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
+• Ixo@aus.edu — International Exchange Office (студенческие обмены); руководитель офиса на сайте не указан (указаны Advisor Grace Morales, Coordinator Lillie De Guzman)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aus.edu/contact-us
 • Https://www.aus.edu/leadership-cabinet/tod-a-laursen
 • Https://www.aus.edu/about/leadership/office-of-the-chancellor/chancellors-staff
 • Https://www.aus.edu/academics/international-study-and-exchange/contact-department-of-international-studies
 • Https://www.aus.edu/the-road-to-launching-nayif-1-the-uaes-first-nanosatellite
-• Https://www.mbrsc.ae/satellites/</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr">
+• Https://www.mbrsc.ae/satellites/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3894,75 +4176,95 @@
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="W8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>Light-1 (2021) — полезная нагрузка RAAD (совместно с Khalifa University)</t>
         </is>
       </c>
-      <c r="X8" s="4" t="inlineStr"/>
       <c r="Y8" s="4" t="inlineStr"/>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr"/>
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• Center for Astrophysics and Space Science (CASS)
 • PhD program in Astrophysics and Space Systems (с 2025)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>• UAE Space Agency (соглашение 2026 по данным Emirates Mars Mission)
 • Khalifa University
 • National Space Science Agency of Bahrain (Light-1)</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
+      <c r="AE8" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Кампус Нью-Йоркского университета (США); NYUAD не ранжируется QS/THE отдельно (рейтинг у NYU в целом)
 • Prof. Fabio Piano — Vice Chancellor с 06.08.2026 (ранее провост 2010–2020)
 • Light-1: NYUAD разработал научную нагрузку RAAD, платформу собирал Khalifa University — спутник засчитан как совместный
 • Отдельный e-mail международного/партнёрского офиса не найден; использован e-mail офиса вице-канцлера. По поиску: общий nyuad@nyu.edu и тел. +971 2 628 4000 (на открытых страницах не подтверждено)
-• Американское юрлицо материнского вуза — возможны ограничения экспортного контроля США при космическом сотрудничестве</t>
-        </is>
-      </c>
-      <c r="AH8" s="4" t="inlineStr">
+• Американское юрлицо материнского вуза — возможны ограничения экспортного контроля США при космическом сотрудничестве
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>• Https://nyuad.nyu.edu/en/about/leadership-and-people/office-of-the-vice-chancellor.html
 • Https://nyuad.nyu.edu/en/research/facilities-and-support/participate-in-research-studies/contacts-and-locations.html
 • Https://nyuad.nyu.edu/en/news/latest-news/science-and-technology/2026/june/nyuad-and-uae-space-agency-cooperation-mars-mission.html
 • Https://nyuad.nyu.edu/en/news/latest-news/science-and-technology/2022/february/cubesat-launch-iss.html
-• Https://www.ku.ac.ae/kustil/news</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr">
+• Https://www.ku.ac.ae/kustil/news
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -4057,70 +4359,90 @@
           <t>President &amp; CEO</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr"/>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="n">
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr">
         <is>
           <t>• HCT-SAT 1 (2025)
 • HCT-SAT 2 (2025)</t>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
       <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
         <is>
           <t>Mohammed Bin Rashid Space Centre (MBRSC)</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="AD9" s="5" t="inlineStr">
+      <c r="AE9" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Канцлер — H.E. Dr. Ahmad Belhoul Al Falasi (министр спорта ОАЭ); исполнительный глава — President &amp; CEO Dr. Faisal Alayyan
 • HCT-SAT 1/2 — 1U CubeSat, построены студентами HCT совместно с MBRSC (MBRSC — сборка, испытания, запуск и связь). HCT-SAT 1 (Transporter-12, 14.01.2025) — по nanosats.csv сигнала нет; HCT-SAT 2 — 28.11.2025, работает
 • Сеть колледжей с кампусами в нескольких эмиратах; на сайте указан только P.O. Box 25026 без эмирата; город (Абу-Даби, центральный офис) — проверить
 • Международного офиса/e-mail не найдено; партнёрства ведёт Partnerships Management Department; использован общий communication@hct.ac.ae
-• Телефон — бесплатная линия ОАЭ 800 663428 (из-за рубежа может не работать)</t>
-        </is>
-      </c>
-      <c r="AH9" s="4" t="inlineStr">
+• Телефон — бесплатная линия ОАЭ 800 663428 (из-за рубежа может не работать)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
         <is>
           <t>• Https://hct.ac.ae/en/about-hct/president-ceos-message/
 • Https://hct.ac.ae/en/about-hct/hct-leadership/
 • Https://hct.ac.ae/en/contact-us/
 • Https://db.satnogs.org/satellite/98470/
 • Https://www.khaleejtimes.com/space/uae-made-mbz-sat-to-blast-off-in-january-2025-from-california
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr">
+• Nanosats.csv
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -4213,68 +4535,87 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
+      <c r="X10" s="4" t="inlineStr"/>
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>MAHASAT — студенческая программа пикоспутников (2023: испытания 5 пикоспутников на дроне-«носителе», не орбитальные)</t>
         </is>
       </c>
-      <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="AA10" s="4" t="inlineStr">
         <is>
           <t>• Centre for Satellite Communications
 • MAHASAT student pico-satellite programme (рук. Mylswamy Annadurai, экс-директор URSC ISRO)</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr"/>
       <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="n">
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="AD10" s="6" t="inlineStr">
+      <c r="AE10" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Кампус индийского BITS Pilani; name_native дан на английском (официальное наименование), арабского официального названия не найдено
 • Директор Prof. Souri Banerjee (назначен в 2024 г., сменил Prof. Srinivasan Madapusi, ныне Pro VC Amity Dubai) — подтверждено Википедией и пресс-релизами, на сайте кампуса имя не найдено
 • E-mail международного офиса не найден; использован e-mail офиса регистратора. Доп. тел. +971 4 275 3711
 • Есть интерес к малым спутникам (MAHASAT, связь с экс-руководством ISRO) — перспективный кандидат при наличии индийских связей
-• Поисковая квота исчерпана — орбитальные запуски MAHASAT после 2023 г. не проверены (в nanosats.csv отсутствуют)</t>
-        </is>
-      </c>
-      <c r="AH10" s="4" t="inlineStr">
+• Поисковая квота исчерпана — орбитальные запуски MAHASAT после 2023 г. не проверены (в nanosats.csv отсутствуют)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI10" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bits-pilani.ac.in/dubai/
 • Https://en.wikipedia.org/wiki/Birla_Institute_of_Technology_and_Science,_Pilani_%E2%80%93_Dubai_Campus
 • Https://gulfnews.com/uae/education/bits-pilani-dubai-campus-appoints-new-director-1.81511128
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -4350,61 +4691,80 @@
           <t>Chief Executive Officer</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="n">
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>Abu Dhabi Quantum Optical Ground Station (ADQOGS) — optical/quantum free-space communications</t>
         </is>
       </c>
-      <c r="Z11" s="4" t="inlineStr">
+      <c r="AA11" s="4" t="inlineStr">
         <is>
           <t>Propulsion and Space Research Center (Chief Researcher Dr. Elias Tsoutsanis)</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="inlineStr"/>
       <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AD11" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="AD11" s="6" t="inlineStr">
+      <c r="AE11" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Не университет — исследовательский центр при ATRC (Advanced Technology Research Council) Абу-Даби, включён намеренно
 • E-mail и телефон на сайте не опубликованы (только веб-форма)
-• Космос: собственных спутников нет; в 2026 г. испытан первый в ОАЭ гибридный суборбитальный ракетный двигатель/ракета; оптическая квантовая наземная станция ADQOGS — потенциальный интерес для связи с CubeSat</t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr">
+• Космос: собственных спутников нет; в 2026 г. испытан первый в ОАЭ гибридный суборбитальный ракетный двигатель/ракета; оптическая квантовая наземная станция ADQOGS — потенциальный интерес для связи с CubeSat
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.tii.ae/contact-us
 • Https://www.tii.ae/about-us
 • Https://www.tii.ae/insights/abu-dhabi-test-launches-first-fully-uae-built-hybrid-rocket-milestone-space-ambitions
-• Https://www.mediaoffice.abudhabi/en/technology/technology-innovation-institute-launches-abu-dhabi-quantum-optical-ground-station/</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr">
+• Https://www.mediaoffice.abudhabi/en/technology/technology-innovation-institute-launches-abu-dhabi-quantum-optical-ground-station/
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4494,53 +4854,67 @@
           <t>THE2027: 301–325</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>1747</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="4" t="inlineStr"/>
       <c r="Z12" s="4" t="inlineStr"/>
       <c r="AA12" s="4" t="inlineStr"/>
       <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="n">
+      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD12" s="7" t="inlineStr">
+      <c r="AE12" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>• Сайт adu.ac.ae рендерится JavaScript — контакты сняты с WSCUC (аккредитатор) и поисковой выдачи
 • По поисковой выдаче: международный офис intl.office@adu.ac.ae, тел. +971 2 501 5555 (на открытой странице не подтверждено)
 • Председатель Попечительского совета — шейх Хамдан бин Заед Аль Нахайян; исполнительный глава — канцлер Prof. Ghassan Aouad
 • Телефон +971 2 501 5717 — из записи WSCUC (может быть не основной номер)
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
-• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
-        </is>
-      </c>
-      <c r="AH12" s="4" t="inlineStr">
+• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI12" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wscuc.org/institutions/abu-dhabi-university/
 • Https://www.mediaoffice.abudhabi/en/education/hamdan-bin-zayed-chairs-1st-abu-dhabi-university-board-of-trustees-meeting-in-2026/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4644,54 +5018,68 @@
           <t>THE2027: 376–400</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="4" t="inlineStr"/>
       <c r="Z13" s="4" t="inlineStr"/>
       <c r="AA13" s="4" t="inlineStr"/>
       <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="n">
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD13" s="7" t="inlineStr">
+      <c r="AE13" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>• Есть Office of International Academic Affairs (OIAA, oiaa.ajman.ac.ae); директор — Victoria Joy Winter (Director of International Academic Affairs, по справочнику сотрудников), e-mail офиса на сайте не опубликован
-• Космических проектов/спутников не найдено (поиск + nanosats.csv)</t>
-        </is>
-      </c>
-      <c r="AH13" s="4" t="inlineStr">
+• Космических проектов/спутников не найдено (поиск + nanosats.csv)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ajman.ac.ae/en/contact-us
 • Https://www.ajman.ac.ae/en/about/message-from-the-chancellor
 • Https://www.ajman.ac.ae/en/directory/staff/victoria-joy-winter
-• Https://oiaa.ajman.ac.ae/en/</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr">
+• Https://oiaa.ajman.ac.ae/en/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ13" s="4" t="inlineStr"/>
+      <c r="AK13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4781,53 +5169,67 @@
           <t>THE2027: 401–450</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>2251</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
       <c r="Z14" s="4" t="inlineStr"/>
       <c r="AA14" s="4" t="inlineStr"/>
       <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="n">
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD14" s="7" t="inlineStr">
+      <c r="AE14" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr"/>
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail и e-mail международного офиса на сайте не опубликованы (только формы); формат адресов сотрудников — имя.фамилия@aau.ac.ae
 • Не путать со спутником Al Ain Sat-1 (AlAinSat-1) — это проект UAE University (NSSTC), а не Al Ain University
 • Абу-Дабийский кампус: тел. +971 2 613 3555
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
-• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
+• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI14" s="4" t="inlineStr">
         <is>
           <t>• Https://aau.ac.ae/en/contact-us
 • Https://aau.ac.ae/en/about-aau/senior-management
 • Https://aau.ac.ae/en/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4921,61 +5323,80 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="n">
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr">
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="4" t="inlineStr">
         <is>
           <t>Department of Aerospace Engineering</t>
         </is>
       </c>
-      <c r="AA15" s="4" t="inlineStr"/>
       <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="n">
+      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AH15" s="4" t="inlineStr">
         <is>
           <t>• Университет принадлежит Emirates Group (государственная группа Дубая); канцлер — шейх Ахмед бин Саид Аль Мактум (председатель Emirates Airline &amp; Group); исполнительный руководитель — вице-канцлер Prof. Ahmad Al Ali
 • Общий адрес почты на домене emirates.com (eau.info@emirates.com); международный офис на сайте не найден
 • Ранее (как Emirates Aviation College) вёлся учебный проект 1U CubeSat (статья IEEE, ~2011); сведений о запуске нет
-• Сайт динамический — страницы руководства не читаются автоматически; руководство подтверждено через Dubai Media Office (июль 2025)</t>
-        </is>
-      </c>
-      <c r="AH15" s="4" t="inlineStr">
+• Сайт динамический — страницы руководства не читаются автоматически; руководство подтверждено через Dubai Media Office (июль 2025)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI15" s="4" t="inlineStr">
         <is>
           <t>• Https://www.eau.ac.ae/contact-us
 • Https://mediaoffice.ae/en/news/2025/july/01-07/emirates-aviation-university-marks-35-years
-• Https://ieeexplore.ieee.org/document/5966842/</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr">
+• Https://ieeexplore.ieee.org/document/5966842/
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4993,25 +5414,188 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
+          <t>American University in Dubai</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>الجامعة الأمريكية في دبي</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Классический</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Частный</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>• Engineering
+• Business Administration
+• Architecture and Design
+• Communication and Media
+• Arts and Sciences
+• Education</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>American University in Dubai, Sheikh Zayed Road, P.O. Box 28282, Dubai, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>info@aud.edu</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Общий ящик университета (General Enquiries)
+Обращение: Dear Director of International Partnerships,</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>info@aud.edu</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>+971 4 399 9000</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>https://www.aud.edu</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Kyle Long</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: =620</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="4" t="inlineStr"/>
+      <c r="Y16" s="4" t="inlineStr"/>
+      <c r="Z16" s="4" t="inlineStr"/>
+      <c r="AA16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AD16" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE16" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t>средняя</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
+        <is>
+          <t>• THE2027: Reporter (без ранга)
+• На сайте есть раздел International Mobility Opportunities, но отдельного e-mail международного офиса нет
+• Спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t>• Https://www.aud.edu/get-in-touch/
+• Https://www.aud.edu/university-overview/aud-leadership/office-of-the-president/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AK16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ОАЭ</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Дубай</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
           <t>Canadian University Dubai</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>الجامعة الكندية دبي</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Другое</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Частный</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>• Engineering &amp; Applied Sciences
 • Business &amp; Management
@@ -5020,17 +5604,17 @@
 • Health Sciences &amp; Psychology</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Canadian University Dubai, City Walk, P.O. Box 117781, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>engagement@cud.ac.ae</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>ФИО не найдено
 Руководитель офиса по партнёрствам
@@ -5038,133 +5622,149 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>engagement@cud.ac.ae</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>info@cud.ac.ae</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+971 4 321 1991</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>https://www.cud.ac.ae</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Prof. Karim Chelli</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>President &amp; Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>QS2027: 616</t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: =616</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr"/>
-      <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="n">
+      <c r="X17" s="4" t="inlineStr"/>
+      <c r="Y17" s="4" t="inlineStr"/>
+      <c r="Z17" s="4" t="inlineStr"/>
+      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD16" s="7" t="inlineStr">
+      <c r="AE17" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>• Engagement@cud.ac.ae — ящик Community Outreach Office для новых коллабораций (тел. +971 4 709 6145); отдельного международного офиса нет
 • Руководитель Community Outreach Office поимённо не указан
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
-• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
-        </is>
-      </c>
-      <c r="AH16" s="4" t="inlineStr">
+• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cud.ac.ae/contact
 • Https://www.cud.ac.ae/about/senior-management
 • Https://www.cud.ac.ae/community-outreach/partnerships
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ16" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>ОАЭ</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Дубай</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>University of Dubai</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>جامعة دبي</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Другое</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Частный</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>• Business Administration
 • Information Technology
@@ -5174,17 +5774,17 @@
 • Digital Leadership</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>University of Dubai, Academic City, Emirates Road – Exit 49, Dubai, United Arab Emirates</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>oeir@ud.ac.ae</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>ФИО не найдено
 Директор офиса внешних и международных связей
@@ -5192,138 +5792,151 @@
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>oeir@ud.ac.ae</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>info@ud.ac.ae</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+971 4 556 6800</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>https://ud.ac.ae</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Dr. Eesa Al Bastaki</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="S18" s="4" t="inlineStr">
         <is>
           <t>QS2027: 781–790</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>THE2027: Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="n">
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr"/>
-      <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="inlineStr"/>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="n">
+      <c r="X18" s="4" t="inlineStr"/>
+      <c r="Y18" s="4" t="inlineStr"/>
+      <c r="Z18" s="4" t="inlineStr"/>
+      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD17" s="7" t="inlineStr">
+      <c r="AE18" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AH18" s="4" t="inlineStr">
         <is>
           <t>• Связан с Dubai Chamber; президент Dr. Eesa Al Bastaki — инженер связи, бывший профессор UAEU, почётный председатель IEEE (UAE)
 • Руководитель офиса EIR поимённо не указан; на странице EIR приведены обращения президента и провоста (Prof. Hussain Al Ahmad)
 • THE2027: в статусе Reporter (не ранжирован)
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
-• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)</t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="inlineStr">
+• QS2027 по зеркалу списка QS (qianmu.org, со ссылкой на topuniversities.com)
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI18" s="4" t="inlineStr">
         <is>
           <t>• Https://ud.ac.ae/leadership/
 • Https://ud.ac.ae/about-us/external-and-international-relations-eir/
 • Https://ud.ac.ae/contact/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK18" s="4" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>ОАЭ</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Абу-Даби</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Zayed University</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>جامعة زايد</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Классический</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Государственный (федеральный)</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>• Business
 • Communication and Media Sciences
@@ -5333,145 +5946,163 @@
 • Natural and Health Sciences</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Zayed University, P.O. Box 144534, Abu Dhabi, United Arab Emirates (Dubai campus: P.O. Box 19282, Dubai)</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>info@zu.ac.ae</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>ФИО не найдено
 Общий ящик университета (General Enquiries)
 Обращение: Dear Director of International Partnerships,</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr"/>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>info@zu.ac.ae</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+971 2 599 3111</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>https://www.zu.ac.ae</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Dr. Kevin Hall</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>President &amp; CEO</t>
         </is>
       </c>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: =588</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>THE2027: 501–550</t>
         </is>
       </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>1642</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr"/>
-      <c r="Y18" s="4" t="inlineStr"/>
-      <c r="Z18" s="4" t="inlineStr"/>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="n">
+      <c r="X19" s="4" t="inlineStr"/>
+      <c r="Y19" s="4" t="inlineStr"/>
+      <c r="Z19" s="4" t="inlineStr"/>
+      <c r="AA19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD18" s="7" t="inlineStr">
+      <c r="AE19" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>• Два кампуса: Абу-Даби и Дубай (тел. Дубай +971 4 402 1111)
 • Dr. Kevin Hall назначен President &amp; CEO с 01.11.2025 (бывший президент University of Victoria); председатель совета попечителей — Shamma bint Sohail Al Mazrui (по данным поиска)
 • QS2027: в топ-500 отсутствует (точная позиция не проверена)
-• Международный офис на сайте не найден; спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH18" s="4" t="inlineStr">
+• Международный офис на сайте не найден; спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI19" s="4" t="inlineStr">
         <is>
           <t>• Https://www.zu.ac.ae/main/en/contact_us/index
 • Https://cheknews.ca/former-uvic-president-kevin-hall-named-ceo-of-university-in-dubai-abu-dhabi-1282755/
-• Https://x.com/Zayed_U/status/1975551341188554950</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="inlineStr">
+• Https://x.com/Zayed_U/status/1975551341188554950
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ18" s="4" t="inlineStr"/>
+      <c r="AK19" s="4" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>ОАЭ</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Аджман</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Gulf Medical University</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>جامعة الخليج الطبية</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Медицинский</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Частный</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>• Medicine
 • Dental Medicine
@@ -5481,17 +6112,17 @@
 • Healthcare Management</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Gulf Medical University, P.O. Box 4184, Ajman, United Arab Emirates</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>chancellor@gmu.ac.ae</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Prof. Manda Venkatramana
 Канцлер университета
@@ -5499,130 +6130,147 @@
 Обращение: Dear Professor Venkatramana,</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr"/>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>chancellor@gmu.ac.ae</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>+971 6 743 1333</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>https://gmu.ac.ae</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>Prof. Manda Venkatramana</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>3309</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr"/>
-      <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="4" t="inlineStr"/>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="n">
+      <c r="X20" s="4" t="inlineStr"/>
+      <c r="Y20" s="4" t="inlineStr"/>
+      <c r="Z20" s="4" t="inlineStr"/>
+      <c r="AA20" s="4" t="inlineStr"/>
+      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD19" s="7" t="inlineStr">
+      <c r="AE20" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AH20" s="4" t="inlineStr">
         <is>
           <t>• Частный медицинский университет группы Thumbay (Thumbay Group)
 • Отдельного e-mail международного офиса нет; есть страница «Regional and International Partners». Использован e-mail офиса канцлера
 • Город Аджман указан в русской транскрипции (вне примеров брифа)
 • Медицинский профиль — для CubeSat-проекта релевантна разве что космическая медицина/биология
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH19" s="4" t="inlineStr">
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI20" s="4" t="inlineStr">
         <is>
           <t>• Https://gmu.ac.ae/contact-us/
 • Https://gmu.ac.ae/aboutgmu/office-of-the-chancellor/
 • Https://gmu.ac.ae/aboutgmu/partner-with-us/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ19" s="4" t="inlineStr"/>
+      <c r="AK20" s="4" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>ОАЭ</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Шарджа</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Al Qasimia University</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>جامعة القاسمية</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Гуманитарный</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Государственный (эмират Шарджа)</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>• Islamic Studies (Sharia)
 • Arabic Language &amp; Literature
@@ -5631,69 +6279,79 @@
 • Law</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr"/>
-      <c r="N20" s="4" t="inlineStr"/>
-      <c r="O20" s="4" t="inlineStr"/>
-      <c r="P20" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>https://www.alqasimia.ac.ae</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Prof. Awad Husain AlKhalaf</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="S20" s="4" t="inlineStr"/>
-      <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="4" t="inlineStr"/>
-      <c r="X20" s="4" t="inlineStr"/>
-      <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="4" t="inlineStr"/>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="n">
+      <c r="X21" s="4" t="inlineStr"/>
+      <c r="Y21" s="4" t="inlineStr"/>
+      <c r="Z21" s="4" t="inlineStr"/>
+      <c r="AA21" s="4" t="inlineStr"/>
+      <c r="AB21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AD21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" s="7" t="inlineStr">
+      <c r="AE21" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr"/>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr"/>
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>• Учреждена правителем Шарджи (шейх Султан бин Мухаммад аль-Касими) — тип собственности «эмират Шарджа» вне стандартного списка, проверить
 • Сайт (SharePoint) не публикует адрес/телефон/e-mail в доступном HTML; контакты не найдены, поисковая квота исчерпана
 • Гуманитарно-исламский профиль — низкая релевантность для CubeSat-проекта
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
 • Повторная проверка 04.10.2026: страница Board of Trustees называет канцлером HE Prof. Awad Husain AlKhalaf (без даты); председатель попечительского совета — HE Jamal Salim AL Turaifi. Страницы Contact us и External Cooperation пусты; в настройках сайта только шаблонные заглушки (12345, business@support.com) — не использовать
-• Перепроверка: Канцлер подтверждён на странице попечительского совета (без даты); контакты на сайте по-прежнему не опубликованы — уровень low сохранён</t>
-        </is>
-      </c>
-      <c r="AH20" s="4" t="inlineStr">
+• Перепроверка: Канцлер подтверждён на странице попечительского совета (без даты); контакты на сайте по-прежнему не опубликованы — уровень low сохранён
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI21" s="4" t="inlineStr">
         <is>
           <t>• Https://www.alqasimia.ac.ae/en/AboutAQU/Pages/UniversityChancellor.aspx
 • Https://www.alqasimia.ac.ae/en
@@ -5701,154 +6359,12 @@
 • Https://www.alqasimia.ac.ae/en/AboutAQU/Pages/BOT.aspx</t>
         </is>
       </c>
-      <c r="AI20" s="4" t="inlineStr">
+      <c r="AJ21" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ20" s="4" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>ОАЭ</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Дубай</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>American University in Dubai</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>الجامعة الأمريكية في دبي</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Классический</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Частный</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>• Engineering
-• Business Administration
-• Architecture and Design
-• Communication and Media
-• Arts and Sciences
-• Education</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>American University in Dubai, Sheikh Zayed Road, P.O. Box 28282, Dubai, United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>info@aud.edu</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>ФИО не найдено
-Общий ящик университета (General Enquiries)
-Обращение: Dear Director of International Partnerships,</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr"/>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>info@aud.edu</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>+971 4 399 9000</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>https://www.aud.edu</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>Dr. Kyle Long</t>
-        </is>
-      </c>
-      <c r="R21" s="4" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr"/>
-      <c r="Y21" s="4" t="inlineStr"/>
-      <c r="Z21" s="4" t="inlineStr"/>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE21" s="4" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="AF21" s="4" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="AG21" s="4" t="inlineStr">
-        <is>
-          <t>• THE2027: Reporter (без ранга)
-• На сайте есть раздел International Mobility Opportunities, но отдельного e-mail международного офиса нет
-• Спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>• Https://www.aud.edu/get-in-touch/
-• Https://www.aud.edu/university-overview/aud-leadership/office-of-the-president/</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AJ21" s="4" t="inlineStr"/>
+      <c r="AK21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -5939,41 +6455,46 @@
           <t>President &amp; CEO</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
           <t>THE2027: Reporter (unranked)</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
+      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="inlineStr"/>
       <c r="AA22" s="4" t="inlineStr"/>
       <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="n">
+      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AD22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD22" s="7" t="inlineStr">
+      <c r="AE22" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AH22" s="4" t="inlineStr">
         <is>
           <t>• Сайт aue.ae блокирует автоматический доступ (403) — данные из Википедии и каталога emiratesuniversities.org; требуется ручная проверка
 • THE2027: в статусе Reporter (не ранжирован)
@@ -5981,22 +6502,23 @@
 • Председатель Попечительского совета — ген.-майор Ahmed Nasser Al-Raisi (по Википедии)
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
 • По поиску на aue.ae есть страница President's Message (aue.ae/presidents-message/) — открыть не удалось (403)
-• Перепроверка: 04.10.2026: aue.ae по-прежнему 403; президент Prof. Muthanna G. Abdul Razzaq подтверждается только поиском — данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH22" s="4" t="inlineStr">
+• Перепроверка: 04.10.2026: aue.ae по-прежнему 403; президент Prof. Muthanna G. Abdul Razzaq подтверждается только поиском — данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI22" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/American_University_in_the_Emirates
 • Https://emiratesuniversities.org/listing/american-emirates/
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI22" s="4" t="inlineStr">
+      <c r="AJ22" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ22" s="4" t="inlineStr"/>
+      <c r="AK22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -6090,60 +6612,79 @@
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="S23" s="4" t="inlineStr"/>
-      <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="n">
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
       <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
       <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="n">
+      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AD23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" s="7" t="inlineStr">
+      <c r="AE23" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AH23" s="4" t="inlineStr">
         <is>
           <t>• Кампус индийской Amity University; в UAE лицензирован CAA
 • Есть бакалавриат Aerospace Engineering (B.Tech/BSc) — релевантная база для CubeSat-сотрудничества
 • Pro Vice Chancellor Prof. Madapusi Srinivasan курирует, в т.ч., международные партнёрства (по его биографии) — альтернативный адресат
 • Отдельного e-mail международного офиса нет; использован info@
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH23" s="4" t="inlineStr">
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI23" s="4" t="inlineStr">
         <is>
           <t>• Https://amityuniversity.ae/contact-us
 • Https://amityuniversity.ae/about-amity/leadership-team/senior-leadership
 • Https://amityuniversity.ae/about-amity/vice-chancellor-s-message
 • Https://www.amityuniversity.ae/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI23" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ23" s="4" t="inlineStr"/>
+      <c r="AK23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -6233,56 +6774,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="n">
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="inlineStr"/>
       <c r="AA24" s="4" t="inlineStr"/>
       <c r="AB24" s="4" t="inlineStr"/>
-      <c r="AC24" s="4" t="n">
+      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" s="7" t="inlineStr">
+      <c r="AE24" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AH24" s="4" t="inlineStr">
         <is>
           <t>• THE2027: Reporter (без ранга)
 • Председатель совета попечителей — шейх Рашид бин Хумаид Аль Нуайми; президент — Mr. Imran Khan (без учёной степени на сайте)
 • Официальное арабское название на сайте не найдено
-• Космической активности нет; nanosats.csv (UAE): записей нет</t>
-        </is>
-      </c>
-      <c r="AH24" s="4" t="inlineStr">
+• Космической активности нет; nanosats.csv (UAE): записей нет
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI24" s="4" t="inlineStr">
         <is>
           <t>• Https://cu.ac.ae/contact-us/
-• Https://cu.ac.ae/about-us/</t>
-        </is>
-      </c>
-      <c r="AI24" s="4" t="inlineStr">
+• Https://cu.ac.ae/about-us/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ24" s="4" t="inlineStr"/>
+      <c r="AK24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -6369,65 +6930,81 @@
       </c>
       <c r="Q25" s="4" t="inlineStr"/>
       <c r="R25" s="4" t="inlineStr"/>
-      <c r="S25" s="4" t="inlineStr"/>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
-          <t>THE2027: Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="n">
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
       <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="n">
+      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AD25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" s="7" t="inlineStr">
+      <c r="AE25" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>• Бывший Dubai Medical College for Girls; официальный сайт — dmu.ae (НЕ dmu.ac.ae — это De Montfort University Dubai)
 • Исполнительный глава (канцлер/президент) на сайте не найден; Vice Chancellor – Academic Affairs: Prof. Sherief Khalifa. По Википедии: председатель — Saeed Bin Ahmed Al Lootah, декан — Prof. Mohammed Galal El Din
 • На странице Board of Trustees первым указан H.E. Lt. Gen. Dhahi Khalfan Tamim (роль председатель/зампред — уточнить)
 • THE2027: в статусе Reporter (не ранжирован)
 • Телефон — бесплатная линия ОАЭ, из-за рубежа может не работать
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH25" s="4" t="inlineStr">
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI25" s="4" t="inlineStr">
         <is>
           <t>• Https://dmu.ae/home/contact-us/
 • Https://dmu.ae/home/vca-message/
 • Https://dmu.ae/home/board-of-trustees/
 • Https://en.wikipedia.org/wiki/Dubai_Medical_University
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI25" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ25" s="4" t="inlineStr"/>
+      <c r="AK25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -6521,58 +7098,77 @@
           <t>Vice Chancellor</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="n">
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
       <c r="AB26" s="4" t="inlineStr"/>
-      <c r="AC26" s="4" t="n">
+      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="7" t="inlineStr">
+      <c r="AE26" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG26" s="4" t="inlineStr">
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>• Сайт ecae.ac.ae напрямую из нашей сети недоступен; страницы (главная, About us, Contact us) открыты через r.jina.ai 04.10.2026. Кампусы также в Аль-Айне и Аджмане (здания Teacher Training Institution Минобразования)
 • Председатель совета (по Википедии) — H.E. Sarah Yousef Al Amiri — на открытых страницах не проверено. Отдельный международный офис и его e-mail на сайте не найдены
 • Название на арабском дано по общепринятому написанию — проверить
 • Педагогический колледж (подготовка учителей) — релевантен только для образовательной/просветительской части проекта
 • Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
-• Перепроверка: Сайт ecae.ac.ae открыт через reader-сервис 04.10.2026: Vice Chancellor Dr. May Laith Al Taee, info@ecae.ac.ae, тел. +971 2 509 9888 и адрес кампуса (Khalifa City, Абу-Даби) подтверждены; дата страницы руководства не указана</t>
-        </is>
-      </c>
-      <c r="AH26" s="4" t="inlineStr">
+• Перепроверка: Сайт ecae.ac.ae открыт через reader-сервис 04.10.2026: Vice Chancellor Dr. May Laith Al Taee, info@ecae.ac.ae, тел. +971 2 509 9888 и адрес кампуса (Khalifa City, Абу-Даби) подтверждены; дата страницы руководства не указана
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI26" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Emirates_College_for_Advanced_Education
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ26" s="4" t="inlineStr"/>
+      <c r="AK26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6658,58 +7254,77 @@
       </c>
       <c r="Q27" s="4" t="inlineStr"/>
       <c r="R27" s="4" t="inlineStr"/>
-      <c r="S27" s="4" t="inlineStr"/>
-      <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="n">
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
       <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="n">
+      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" s="7" t="inlineStr">
+      <c r="AE27" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG27" s="4" t="inlineStr">
+      <c r="AH27" s="4" t="inlineStr">
         <is>
           <t>• Учреждён в 2006 г. в системе ACTVET (Abu Dhabi Centre for Technical and Vocational Education and Training)
 • Кампусы (официальный сайт): Абу-Даби (Al Mafraq, +971 2 507 8765, info@fchs.ac.ae), Эль-Айн (Al Maqam, +971 3 703 5555, alain@fchs.ac.ae), Аль-Дафра (Madinat Zayed, +971 2 898 6915, aldhafra@fchs.ac.ae), Аджман (+971 6 701 7200, ajman@fchs.ac.ae)
 • Руководитель колледжа (декан/директор) на сайте не указан; main_fields — ориентировочно
 • Медицинский колледж; nanosats.csv (UAE): записей нет
-• Перепроверка: Общий e-mail info@fchs.ac.ae, телефон и кампусы подтверждены через официальный API сайта fchs.ac.ae (обновл. 06.2026); руководитель не найден</t>
-        </is>
-      </c>
-      <c r="AH27" s="4" t="inlineStr">
+• Перепроверка: Общий e-mail info@fchs.ac.ae, телефон и кампусы подтверждены через официальный API сайта fchs.ac.ae (обновл. 06.2026); руководитель не найден
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI27" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fchs.ac.ae/contact-us
 • Https://www.fchs.ac.ae/
-• Https://www.fchs.ac.ae/api/campuses</t>
-        </is>
-      </c>
-      <c r="AI27" s="4" t="inlineStr">
+• Https://www.fchs.ac.ae/api/campuses
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ27" s="4" t="inlineStr"/>
+      <c r="AK27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6789,54 +7404,73 @@
           <t>Provost and Vice-Principal (Dubai)</t>
         </is>
       </c>
-      <c r="S28" s="4" t="inlineStr"/>
-      <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="4" t="n">
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
       <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="n">
+      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AD28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" s="7" t="inlineStr">
+      <c r="AE28" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr"/>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr"/>
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
+      <c r="AH28" s="4" t="inlineStr">
         <is>
           <t>• Кампус британского Heriot-Watt University (Эдинбург); в рейтингах QS/THE учитывается в составе головного вуза (Великобритания), отдельно не ранжируется
 • Общий e-mail на сайте не опубликован (только формы) — рекомендуется обращение через Provost
 • Профиль: инженерия/энергетика, профиль_type условно technical
 • Решения о партнёрствах могут требовать согласования с головным вузом в Великобритании
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH28" s="4" t="inlineStr">
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI28" s="4" t="inlineStr">
         <is>
           <t>• Https://www.hw.ac.uk/dubai/about
 • Https://www.hw.ac.uk/dubai/about/provost-and-vice-principal
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI28" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ28" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ28" s="4" t="inlineStr"/>
+      <c r="AK28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6911,52 +7545,62 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S29" s="4" t="inlineStr"/>
-      <c r="T29" s="4" t="inlineStr"/>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter (в списке, без места)</t>
+        </is>
+      </c>
       <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="n">
+      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
       <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="n">
+      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AD29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" s="7" t="inlineStr">
+      <c r="AE29" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE29" s="4" t="inlineStr"/>
-      <c r="AF29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr"/>
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG29" s="4" t="inlineStr">
+      <c r="AH29" s="4" t="inlineStr">
         <is>
           <t>• Кампусы в Абу-Даби и Эль-Айне (новый кампус в Эль-Айне открыт в 2025)
 • Main_fields — ориентировочно, не проверены по сайту
 • THE2027: Reporter (без ранга); nanosats.csv (UAE): записей нет
 • Сайт lu.ac.ae по-прежнему за Cloudflare (403, 04.10.2026). По поисковому индексу официальных страниц (lu.ac.ae/our-leadership, профиль вуза): президент Prof. Mohamed Mahjoub Dhiaf, адрес Baniyas Tower B, Al Danah, P.O. Box 41009, Abu Dhabi, тел. 600 500606; e-mail в сниппете скрыт — не внесён (старый info@lc.ac.ae из Википедии не использовать без проверки)
-• Перепроверка: Сайт закрыт Cloudflare; по поисковому индексу официальных страниц уточнены полное имя президента и адрес; e-mail не подтверждён</t>
-        </is>
-      </c>
-      <c r="AH29" s="4" t="inlineStr">
+• Перепроверка: Сайт закрыт Cloudflare; по поисковому индексу официальных страниц уточнены полное имя президента и адрес; e-mail не подтверждён
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI29" s="4" t="inlineStr">
         <is>
           <t>Https://www.education-uae.com/liwa-university-al-ain-campus-launch/</t>
         </is>
       </c>
-      <c r="AI29" s="4" t="inlineStr">
+      <c r="AJ29" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ29" s="4" t="inlineStr"/>
+      <c r="AK29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -7051,60 +7695,79 @@
           <t>Pro Vice Chancellor – MAHE Dubai</t>
         </is>
       </c>
-      <c r="S30" s="4" t="inlineStr"/>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="n">
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
       <c r="AB30" s="4" t="inlineStr"/>
-      <c r="AC30" s="4" t="n">
+      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AD30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD30" s="7" t="inlineStr">
+      <c r="AE30" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
+      <c r="AH30" s="4" t="inlineStr">
         <is>
           <t>• Кампус индийской Manipal Academy of Higher Education (MAHE); Vice Chancellor MAHE — Dr. Sharath Kumar Rao K (Индия)
 • Сайт прямо указывает: по академическим/институциональным вопросам обращаться к Dr. Sudhindra — sudhindra.shamanna@manipaldubai.com
 • Name_native дан на английском (официальное название); арабского официального не найдено
 • Dr. Sudhindra — отставной полковник индийской армии (EME), PhD IIT Madras
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH30" s="4" t="inlineStr">
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1.; Кампус MAHE в Дубае; глобальные рейтинги ранжируют MAHE (Индия) целиком</t>
+        </is>
+      </c>
+      <c r="AI30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.manipaldubai.com/
 • Https://www.manipaldubai.com/contact-us
 • Https://www.manipaldubai.com/leadership
 • Https://www.manipaldubai.com/international-collaborations
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI30" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ30" s="4" t="inlineStr"/>
+      <c r="AK30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -7198,54 +7861,73 @@
           <t>Provost and Director</t>
         </is>
       </c>
-      <c r="S31" s="4" t="inlineStr"/>
-      <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="n">
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
       <c r="AB31" s="4" t="inlineStr"/>
-      <c r="AC31" s="4" t="n">
+      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AD31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD31" s="7" t="inlineStr">
+      <c r="AE31" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
+      <c r="AH31" s="4" t="inlineStr">
         <is>
           <t>• Кампус британского Middlesex University (Лондон); партнёрские решения могут требовать согласования с головным вузом
-• Main_fields — ориентировочно; nanosats.csv (UAE): записей нет</t>
-        </is>
-      </c>
-      <c r="AH31" s="4" t="inlineStr">
+• Main_fields — ориентировочно; nanosats.csv (UAE): записей нет
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI31" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mdx.ac.ae/contact-us
-• Https://www.mdx.ac.ae/about-us/our-people</t>
-        </is>
-      </c>
-      <c r="AI31" s="4" t="inlineStr">
+• Https://www.mdx.ac.ae/about-us/our-people
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ31" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ31" s="4" t="inlineStr"/>
+      <c r="AK31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -7321,54 +8003,64 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr"/>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="n">
+      <c r="V32" s="4" t="inlineStr"/>
+      <c r="W32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
       <c r="AB32" s="4" t="inlineStr"/>
-      <c r="AC32" s="4" t="n">
+      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AD32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD32" s="7" t="inlineStr">
+      <c r="AE32" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr"/>
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
+      <c r="AH32" s="4" t="inlineStr">
         <is>
           <t>• Сайт mbzuai.ac.ae заблокирован Cloudflare (403) — контакты не проверены напрямую
 • По поисковой выдаче страницы mbzuai.ac.ae/about/contact: info@mbzuai.ac.ae, тел. +971 2 811 3333 (не подтверждено открытием страницы)
 • Председатель Попечительского совета — Khaldoon Khalifa Al Mubarak; президент — Prof. Eric Xing (с 2021)
 • Космических проектов не найдено; интерес — ИИ для обработки спутниковых данных/автономия бортовых систем
-• Узкопрофильный вуз (только ИИ), profile_type условно technical</t>
-        </is>
-      </c>
-      <c r="AH32" s="4" t="inlineStr">
+• Узкопрофильный вуз (только ИИ), profile_type условно technical
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI32" s="4" t="inlineStr">
         <is>
           <t>• Https://en.wikipedia.org/wiki/Mohamed_bin_Zayed_University_of_Artificial_Intelligence
 • Https://library.mbzuai.ac.ae/contact-us
 • Https://www.mediaoffice.abudhabi/en/education/mbzuai-appoints-world-renowned-leading-ai/</t>
         </is>
       </c>
-      <c r="AI32" s="4" t="inlineStr">
+      <c r="AJ32" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ32" s="4" t="inlineStr"/>
+      <c r="AK32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -7461,57 +8153,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S33" s="4" t="inlineStr"/>
-      <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="n">
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
       <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="n">
+      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AD33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD33" s="7" t="inlineStr">
+      <c r="AE33" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE33" s="4" t="inlineStr">
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF33" s="4" t="inlineStr">
+      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
+      <c r="AH33" s="4" t="inlineStr">
         <is>
           <t>• Входит в Dubai Health (государственная академическая система здравоохранения Дубая); канцлер — шейх Ахмед бин Саид Аль Мактум
 • Есть Vice President - Partnerships: Isabel Jennings (e-mail не опубликован) — логичный адресат по партнёрствам
 • Телефон опубликован только как бесплатный номер 800 MBRU (6278)
-• Медицинский профиль; nanosats.csv (UAE): записей нет</t>
-        </is>
-      </c>
-      <c r="AH33" s="4" t="inlineStr">
+• Медицинский профиль; nanosats.csv (UAE): записей нет
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1. Этот вуз — в Group 1 (Outstanding), места внутри групп нет</t>
+        </is>
+      </c>
+      <c r="AI33" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mbru.ac.ae/contact-us/
 • Https://www.mbru.ac.ae/about-mbru/our-leadership/
-• Https://www.mbru.ac.ae/about-mbru/</t>
-        </is>
-      </c>
-      <c r="AI33" s="4" t="inlineStr">
+• Https://www.mbru.ac.ae/about-mbru/
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ33" s="4" t="inlineStr"/>
+      <c r="AK33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -7600,54 +8311,73 @@
           <t>Dean and Academic President</t>
         </is>
       </c>
-      <c r="S34" s="4" t="inlineStr"/>
-      <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="n">
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
       <c r="AB34" s="4" t="inlineStr"/>
-      <c r="AC34" s="4" t="n">
+      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AD34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD34" s="7" t="inlineStr">
+      <c r="AE34" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF34" s="4" t="inlineStr">
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
+      <c r="AH34" s="4" t="inlineStr">
         <is>
           <t>• Кампус австралийского Murdoch University (Перт)
-• Main_fields — ориентировочно; nanosats.csv (UAE): записей нет</t>
-        </is>
-      </c>
-      <c r="AH34" s="4" t="inlineStr">
+• Main_fields — ориентировочно; nanosats.csv (UAE): записей нет
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI34" s="4" t="inlineStr">
         <is>
           <t>• Https://www.murdochuniversitydubai.com/
-• Https://www.murdochuniversitydubai.com/explore/about/</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="inlineStr">
+• Https://www.murdochuniversitydubai.com/explore/about/
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ34" s="4" t="inlineStr"/>
+      <c r="AK34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -7740,56 +8470,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S35" s="4" t="inlineStr"/>
-      <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="n">
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="inlineStr"/>
       <c r="AA35" s="4" t="inlineStr"/>
       <c r="AB35" s="4" t="inlineStr"/>
-      <c r="AC35" s="4" t="n">
+      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AD35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD35" s="7" t="inlineStr">
+      <c r="AE35" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE35" s="4" t="inlineStr">
+      <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF35" s="4" t="inlineStr">
+      <c r="AG35" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG35" s="4" t="inlineStr">
+      <c r="AH35" s="4" t="inlineStr">
         <is>
           <t>• Основан в 2006 г. под патронатом правителя Рас-эль-Хаймы шейха Сауда бин Сакра Аль-Касими; форма собственности на сайте явно не указана
 • THE2027: Reporter (без ранга)
-• Медицинский профиль — космическая тематика маловероятна; nanosats.csv (UAE): записей нет</t>
-        </is>
-      </c>
-      <c r="AH35" s="4" t="inlineStr">
+• Медицинский профиль — космическая тематика маловероятна; nanosats.csv (UAE): записей нет
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI35" s="4" t="inlineStr">
         <is>
           <t>• Https://www.rakmhsu.ac.ae/contact
 • Https://www.rakmhsu.ac.ae/university-leadership
-• Https://www.rakmhsu.ac.ae/about</t>
-        </is>
-      </c>
-      <c r="AI35" s="4" t="inlineStr">
+• Https://www.rakmhsu.ac.ae/about
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ35" s="4" t="inlineStr"/>
+      <c r="AK35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -7883,63 +8633,79 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S36" s="4" t="inlineStr"/>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>THE2027: Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="n">
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="4" t="inlineStr"/>
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="inlineStr"/>
       <c r="AA36" s="4" t="inlineStr"/>
       <c r="AB36" s="4" t="inlineStr"/>
-      <c r="AC36" s="4" t="n">
+      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AD36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD36" s="7" t="inlineStr">
+      <c r="AE36" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE36" s="4" t="inlineStr">
+      <c r="AF36" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF36" s="4" t="inlineStr">
+      <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG36" s="4" t="inlineStr">
+      <c r="AH36" s="4" t="inlineStr">
         <is>
           <t>• Академия безопасности, обороны и кризисного управления; учреждена Законом № 7 от 2013 г. (шейх Халифа бин Заед) — тип собственности «эмират Абу-Даби» — проверить
 • Учёная степень/титул президента на странице не указаны — обращение без «Prof./Dr.»
 • Оборонно-силовой профиль — учитывать чувствительность сотрудничества
 • THE2027: в статусе Reporter (не ранжирован)
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH36" s="4" t="inlineStr">
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI36" s="4" t="inlineStr">
         <is>
           <t>• Https://www.ra.ac.ae/en/about-rabdan/leadership-team
 • Https://www.ra.ac.ae/en/contact-us
 • Https://www.ra.ac.ae/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI36" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ36" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ36" s="4" t="inlineStr"/>
+      <c r="AK36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -8028,56 +8794,75 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S37" s="4" t="inlineStr"/>
-      <c r="T37" s="4" t="inlineStr"/>
-      <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="4" t="n">
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W37" s="4" t="inlineStr"/>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="inlineStr"/>
       <c r="AA37" s="4" t="inlineStr"/>
       <c r="AB37" s="4" t="inlineStr"/>
-      <c r="AC37" s="4" t="n">
+      <c r="AC37" s="4" t="inlineStr"/>
+      <c r="AD37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD37" s="7" t="inlineStr">
+      <c r="AE37" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE37" s="4" t="inlineStr">
+      <c r="AF37" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF37" s="4" t="inlineStr">
+      <c r="AG37" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG37" s="4" t="inlineStr">
+      <c r="AH37" s="4" t="inlineStr">
         <is>
           <t>• Глобальный кампус RIT (Рочестер, США), отчитывается перед RIT NY; совет директоров включает представителей Dubai Silicon Oasis Authority
 • Сведения о спутниках RIT Dubai не найдены; nanosats.csv (UAE): записей нет
-• Арабское официальное название на сайте не найдено</t>
-        </is>
-      </c>
-      <c r="AH37" s="4" t="inlineStr">
+• Арабское официальное название на сайте не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI37" s="4" t="inlineStr">
         <is>
           <t>• Https://www.rit.edu/dubai/
 • Https://www.rit.edu/dubai/about-rit
-• Https://www.rit.edu/dubai/board-directors</t>
-        </is>
-      </c>
-      <c r="AI37" s="4" t="inlineStr">
+• Https://www.rit.edu/dubai/board-directors
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ37" s="4" t="inlineStr"/>
+      <c r="AK37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -8157,59 +8942,75 @@
           <t>Chancellor</t>
         </is>
       </c>
-      <c r="S38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>THE2027: Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="4" t="n">
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="inlineStr"/>
       <c r="AA38" s="4" t="inlineStr"/>
       <c r="AB38" s="4" t="inlineStr"/>
-      <c r="AC38" s="4" t="n">
+      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AD38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD38" s="7" t="inlineStr">
+      <c r="AE38" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE38" s="4" t="inlineStr"/>
-      <c r="AF38" s="4" t="inlineStr">
+      <c r="AF38" s="4" t="inlineStr"/>
+      <c r="AG38" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG38" s="4" t="inlineStr">
+      <c r="AH38" s="4" t="inlineStr">
         <is>
           <t>• Кампус французских университетов (Sorbonne Université, Université Paris Cité и др.), финансируется правительством Абу-Даби — тип «кампус иностранного вуза» условен
 • E-mail на сайте не опубликован (только формы); второй телефон +971 2 656 9555
 • Есть магистратура «International Law, Spaces and Sovereignty» — возможная точка входа по космическому праву
 • THE2027: в статусе Reporter (не ранжирован)
-• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH38" s="4" t="inlineStr">
+• Космическая активность: по nanosats.csv (ОАЭ) и быстрому поиску спутников не найдено
+• Рейтинги: Есть только National HEI Classification Framework (МинОбр ОАЭ, 06.2024): 4 группы без мест; публично названы лишь вузы Group 1</t>
+        </is>
+      </c>
+      <c r="AI38" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sorbonne.ae/about-us/governance/university-leadership
 • Https://www.sorbonne.ae/contact-us
 • Https://www.sorbonne.ae/
-• Nanosats.csv</t>
-        </is>
-      </c>
-      <c r="AI38" s="4" t="inlineStr">
+• Nanosats.csv
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://www.moe.gov.ae/En/MediaCenter/News/pages/heis-classification.aspx</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ38" s="4" t="inlineStr"/>
+      <c r="AK38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -8300,55 +9101,65 @@
           <t>Vice-Chancellor</t>
         </is>
       </c>
-      <c r="S39" s="4" t="inlineStr"/>
-      <c r="T39" s="4" t="inlineStr"/>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter (в списке, без места)</t>
+        </is>
+      </c>
       <c r="U39" s="4" t="inlineStr"/>
-      <c r="V39" s="4" t="n">
+      <c r="V39" s="4" t="inlineStr"/>
+      <c r="W39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W39" s="4" t="inlineStr"/>
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="inlineStr"/>
       <c r="AA39" s="4" t="inlineStr"/>
       <c r="AB39" s="4" t="inlineStr"/>
-      <c r="AC39" s="4" t="n">
+      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AD39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD39" s="7" t="inlineStr">
+      <c r="AE39" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE39" s="4" t="inlineStr">
+      <c r="AF39" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF39" s="4" t="inlineStr">
+      <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG39" s="4" t="inlineStr">
+      <c r="AH39" s="4" t="inlineStr">
         <is>
           <t>• Сайт buid.ac.ae блокирует автоматический доступ (403); контакты взяты из Undergraduate Student Handbook (сент. 2026)
 • Канцлер — шейх Ахмед бин Саид Аль Мактум
-• THE2027: Reporter (без ранга); nanosats.csv (UAE): записей нет</t>
-        </is>
-      </c>
-      <c r="AH39" s="4" t="inlineStr">
+• THE2027: Reporter (без ранга); nanosats.csv (UAE): записей нет
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI39" s="4" t="inlineStr">
         <is>
           <t>• Https://www.buid.ac.ae/wp-content/uploads/Handbooks/UG-Handbook.pdf
 • Https://mediaoffice.ae/en/news/2026/april/30-04/the-community-development-authority-in-dubai-and-the-british-university-in-dubai-sign</t>
         </is>
       </c>
-      <c r="AI39" s="4" t="inlineStr">
+      <c r="AJ39" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ39" s="4" t="inlineStr"/>
+      <c r="AK39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8423,55 +9234,65 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S40" s="4" t="inlineStr"/>
-      <c r="T40" s="4" t="inlineStr"/>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="4" t="n">
+      <c r="V40" s="4" t="inlineStr"/>
+      <c r="W40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="4" t="inlineStr"/>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="inlineStr"/>
       <c r="AA40" s="4" t="inlineStr"/>
       <c r="AB40" s="4" t="inlineStr"/>
-      <c r="AC40" s="4" t="n">
+      <c r="AC40" s="4" t="inlineStr"/>
+      <c r="AD40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD40" s="7" t="inlineStr">
+      <c r="AE40" s="7" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE40" s="4" t="inlineStr"/>
-      <c r="AF40" s="4" t="inlineStr">
+      <c r="AF40" s="4" t="inlineStr"/>
+      <c r="AG40" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG40" s="4" t="inlineStr">
+      <c r="AH40" s="4" t="inlineStr">
         <is>
           <t>• Сайт uowdubai.ac.ae блокирует автоматический доступ (403) — e-mail, телефон и P.O. Box не проверены
 • Автономный кампус University of Wollongong (Австралия), президент с 2015 г
 • Main_fields — ориентировочно; nanosats.csv (UAE): записей нет
-• Перепроверка: uowdubai.ac.ae (главная, /contact-us, sitemap) и WebFetch возвращают 403 — данные не изменены (04.10.2026)</t>
-        </is>
-      </c>
-      <c r="AH40" s="4" t="inlineStr">
+• Перепроверка: uowdubai.ac.ae (главная, /contact-us, sitemap) и WebFetch возвращают 403 — данные не изменены (04.10.2026)
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI40" s="4" t="inlineStr">
         <is>
           <t>• Https://www.uow.edu.au/the-stand/2025/branching-out-growing-uows-global-reach-in-dubai.php
 • Https://en.wikipedia.org/wiki/University_of_Wollongong_in_Dubai</t>
         </is>
       </c>
-      <c r="AI40" s="4" t="inlineStr">
+      <c r="AJ40" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ40" s="4" t="inlineStr"/>
+      <c r="AK40" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ40"/>
+  <autoFilter ref="A1:AK40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>